--- a/research/traditional_assets/database/data/kuwait/kuwait_transportation.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_transportation.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0890190790910044</v>
+        <v>0.08892380047236789</v>
       </c>
       <c r="C2">
-        <v>6953.60805824434</v>
+        <v>6895.214797465725</v>
       </c>
       <c r="D2">
-        <v>6222.10805824434</v>
+        <v>6232.738797465726</v>
       </c>
       <c r="E2">
-        <v>-4857.1</v>
+        <v>-4788.076</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>69.024</v>
       </c>
       <c r="G2">
         <v>731.5</v>
@@ -1451,28 +1451,28 @@
         <v>488</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.4719072</v>
       </c>
       <c r="N2">
-        <v>488</v>
+        <v>484.5280928</v>
       </c>
       <c r="O2">
-        <v>73.2</v>
+        <v>72.67921392</v>
       </c>
       <c r="P2">
-        <v>414.8</v>
+        <v>411.84887888</v>
       </c>
       <c r="Q2">
-        <v>730.8</v>
+        <v>727.84887888</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0890190790910044</v>
+        <v>0.08939015199229081</v>
       </c>
       <c r="T2">
-        <v>0.8198499599185861</v>
+        <v>0.8268890757360688</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>140.5567522081236</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08892380047236789</v>
+        <v>0.08882852185373138</v>
       </c>
       <c r="C3">
-        <v>6895.214797465725</v>
+        <v>6836.857925008468</v>
       </c>
       <c r="D3">
-        <v>6232.738797465726</v>
+        <v>6243.405925008467</v>
       </c>
       <c r="E3">
-        <v>-4788.076</v>
+        <v>-4719.052000000001</v>
       </c>
       <c r="F3">
-        <v>69.024</v>
+        <v>138.048</v>
       </c>
       <c r="G3">
         <v>731.5</v>
@@ -1533,28 +1533,28 @@
         <v>488</v>
       </c>
       <c r="M3">
-        <v>3.4719072</v>
+        <v>6.9438144</v>
       </c>
       <c r="N3">
-        <v>484.5280928</v>
+        <v>481.0561856</v>
       </c>
       <c r="O3">
-        <v>72.67921392</v>
+        <v>72.15842784</v>
       </c>
       <c r="P3">
-        <v>411.84887888</v>
+        <v>408.89775776</v>
       </c>
       <c r="Q3">
-        <v>727.84887888</v>
+        <v>724.89775776</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08939015199229081</v>
+        <v>0.08976879780993</v>
       </c>
       <c r="T3">
-        <v>0.8268890757360688</v>
+        <v>0.8340718469783984</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>140.5567522081236</v>
+        <v>70.27837610406176</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08882852185373138</v>
+        <v>0.08873324323509486</v>
       </c>
       <c r="C4">
-        <v>6836.857925008468</v>
+        <v>6778.53762802512</v>
       </c>
       <c r="D4">
-        <v>6243.405925008467</v>
+        <v>6254.10962802512</v>
       </c>
       <c r="E4">
-        <v>-4719.052000000001</v>
+        <v>-4650.028</v>
       </c>
       <c r="F4">
-        <v>138.048</v>
+        <v>207.072</v>
       </c>
       <c r="G4">
         <v>731.5</v>
@@ -1615,28 +1615,28 @@
         <v>488</v>
       </c>
       <c r="M4">
-        <v>6.9438144</v>
+        <v>10.4157216</v>
       </c>
       <c r="N4">
-        <v>481.0561856</v>
+        <v>477.5842784</v>
       </c>
       <c r="O4">
-        <v>72.15842784</v>
+        <v>71.63764175999999</v>
       </c>
       <c r="P4">
-        <v>408.89775776</v>
+        <v>405.94663664</v>
       </c>
       <c r="Q4">
-        <v>724.89775776</v>
+        <v>721.94663664</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08976879780993</v>
+        <v>0.09015525075782976</v>
       </c>
       <c r="T4">
-        <v>0.8340718469783984</v>
+        <v>0.8414027165968582</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>70.27837610406176</v>
+        <v>46.85225073604119</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08873324323509486</v>
+        <v>0.08863796461645837</v>
       </c>
       <c r="C5">
-        <v>6778.53762802512</v>
+        <v>6720.254094953856</v>
       </c>
       <c r="D5">
-        <v>6254.10962802512</v>
+        <v>6264.850094953856</v>
       </c>
       <c r="E5">
-        <v>-4650.028</v>
+        <v>-4581.004000000001</v>
       </c>
       <c r="F5">
-        <v>207.072</v>
+        <v>276.096</v>
       </c>
       <c r="G5">
         <v>731.5</v>
@@ -1697,28 +1697,28 @@
         <v>488</v>
       </c>
       <c r="M5">
-        <v>10.4157216</v>
+        <v>13.8876288</v>
       </c>
       <c r="N5">
-        <v>477.5842784</v>
+        <v>474.1123712</v>
       </c>
       <c r="O5">
-        <v>71.63764175999999</v>
+        <v>71.11685568</v>
       </c>
       <c r="P5">
-        <v>405.94663664</v>
+        <v>402.99551552</v>
       </c>
       <c r="Q5">
-        <v>721.94663664</v>
+        <v>718.99551552</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09015525075782976</v>
+        <v>0.09054975480881081</v>
       </c>
       <c r="T5">
-        <v>0.8414027165968582</v>
+        <v>0.8488863126657027</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>46.85225073604119</v>
+        <v>35.13918805203088</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08863796461645837</v>
+        <v>0.08854268599782186</v>
       </c>
       <c r="C6">
-        <v>6720.254094953856</v>
+        <v>6662.007515529531</v>
       </c>
       <c r="D6">
-        <v>6264.850094953856</v>
+        <v>6275.627515529531</v>
       </c>
       <c r="E6">
-        <v>-4581.004000000001</v>
+        <v>-4511.98</v>
       </c>
       <c r="F6">
-        <v>276.096</v>
+        <v>345.1200000000001</v>
       </c>
       <c r="G6">
         <v>731.5</v>
@@ -1779,28 +1779,28 @@
         <v>488</v>
       </c>
       <c r="M6">
-        <v>13.8876288</v>
+        <v>17.359536</v>
       </c>
       <c r="N6">
-        <v>474.1123712</v>
+        <v>470.640464</v>
       </c>
       <c r="O6">
-        <v>71.11685568</v>
+        <v>70.59606959999999</v>
       </c>
       <c r="P6">
-        <v>402.99551552</v>
+        <v>400.0443944</v>
       </c>
       <c r="Q6">
-        <v>718.99551552</v>
+        <v>716.0443944</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09054975480881081</v>
+        <v>0.09095256420823356</v>
       </c>
       <c r="T6">
-        <v>0.8488863126657027</v>
+        <v>0.8565274581254703</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>35.13918805203088</v>
+        <v>28.1113504416247</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08854268599782186</v>
+        <v>0.08844740737918536</v>
       </c>
       <c r="C7">
-        <v>6662.007515529531</v>
+        <v>6603.798080794855</v>
       </c>
       <c r="D7">
-        <v>6275.627515529531</v>
+        <v>6286.442080794855</v>
       </c>
       <c r="E7">
-        <v>-4511.98</v>
+        <v>-4442.956</v>
       </c>
       <c r="F7">
-        <v>345.1200000000001</v>
+        <v>414.1440000000001</v>
       </c>
       <c r="G7">
         <v>731.5</v>
@@ -1861,28 +1861,28 @@
         <v>488</v>
       </c>
       <c r="M7">
-        <v>17.359536</v>
+        <v>20.8314432</v>
       </c>
       <c r="N7">
-        <v>470.640464</v>
+        <v>467.1685568</v>
       </c>
       <c r="O7">
-        <v>70.59606959999999</v>
+        <v>70.07528352</v>
       </c>
       <c r="P7">
-        <v>400.0443944</v>
+        <v>397.0932732799999</v>
       </c>
       <c r="Q7">
-        <v>716.0443944</v>
+        <v>713.0932732799999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09095256420823356</v>
+        <v>0.09136394402040995</v>
       </c>
       <c r="T7">
-        <v>0.8565274581254703</v>
+        <v>0.8643311811482115</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>28.1113504416247</v>
+        <v>23.42612536802059</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08844740737918536</v>
+        <v>0.08835212876054888</v>
       </c>
       <c r="C8">
-        <v>6603.798080794855</v>
+        <v>6545.625983111677</v>
       </c>
       <c r="D8">
-        <v>6286.442080794855</v>
+        <v>6297.293983111676</v>
       </c>
       <c r="E8">
-        <v>-4442.956</v>
+        <v>-4373.932000000001</v>
       </c>
       <c r="F8">
-        <v>414.144</v>
+        <v>483.168</v>
       </c>
       <c r="G8">
         <v>731.5</v>
@@ -1943,28 +1943,28 @@
         <v>488</v>
       </c>
       <c r="M8">
-        <v>20.8314432</v>
+        <v>24.3033504</v>
       </c>
       <c r="N8">
-        <v>467.1685568</v>
+        <v>463.6966496</v>
       </c>
       <c r="O8">
-        <v>70.07528352</v>
+        <v>69.55449743999999</v>
       </c>
       <c r="P8">
-        <v>397.0932732799999</v>
+        <v>394.14215216</v>
       </c>
       <c r="Q8">
-        <v>713.0932732799999</v>
+        <v>710.14215216</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09136394402040995</v>
+        <v>0.09178417071026759</v>
       </c>
       <c r="T8">
-        <v>0.8643311811482115</v>
+        <v>0.8723027261714419</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.42612536802059</v>
+        <v>20.07953602973193</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08835212876054886</v>
+        <v>0.08825685014191235</v>
       </c>
       <c r="C9">
-        <v>6545.625983111678</v>
+        <v>6487.491416172397</v>
       </c>
       <c r="D9">
-        <v>6297.293983111677</v>
+        <v>6308.183416172397</v>
       </c>
       <c r="E9">
-        <v>-4373.932000000001</v>
+        <v>-4304.908</v>
       </c>
       <c r="F9">
-        <v>483.1680000000001</v>
+        <v>552.192</v>
       </c>
       <c r="G9">
         <v>731.5</v>
@@ -2025,28 +2025,28 @@
         <v>488</v>
       </c>
       <c r="M9">
-        <v>24.3033504</v>
+        <v>27.7752576</v>
       </c>
       <c r="N9">
-        <v>463.6966496</v>
+        <v>460.2247424</v>
       </c>
       <c r="O9">
-        <v>69.55449743999999</v>
+        <v>69.03371136</v>
       </c>
       <c r="P9">
-        <v>394.14215216</v>
+        <v>391.19103104</v>
       </c>
       <c r="Q9">
-        <v>710.14215216</v>
+        <v>707.1910310400001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09178417071026759</v>
+        <v>0.09221353276294821</v>
       </c>
       <c r="T9">
-        <v>0.8723027261714419</v>
+        <v>0.880447565651699</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.07953602973193</v>
+        <v>17.56959402601544</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08825685014191235</v>
+        <v>0.08816157152327583</v>
       </c>
       <c r="C10">
-        <v>6487.491416172397</v>
+        <v>6429.394575011484</v>
       </c>
       <c r="D10">
-        <v>6308.183416172397</v>
+        <v>6319.110575011485</v>
       </c>
       <c r="E10">
-        <v>-4304.908</v>
+        <v>-4235.884</v>
       </c>
       <c r="F10">
-        <v>552.192</v>
+        <v>621.216</v>
       </c>
       <c r="G10">
         <v>731.5</v>
@@ -2107,28 +2107,28 @@
         <v>488</v>
       </c>
       <c r="M10">
-        <v>27.7752576</v>
+        <v>31.2471648</v>
       </c>
       <c r="N10">
-        <v>460.2247424</v>
+        <v>456.7528352</v>
       </c>
       <c r="O10">
-        <v>69.03371136</v>
+        <v>68.51292527999999</v>
       </c>
       <c r="P10">
-        <v>391.19103104</v>
+        <v>388.23990992</v>
       </c>
       <c r="Q10">
-        <v>707.1910310400001</v>
+        <v>704.2399099199999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09221353276294821</v>
+        <v>0.09265233134425915</v>
       </c>
       <c r="T10">
-        <v>0.880447565651699</v>
+        <v>0.8887714125930606</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.56959402601544</v>
+        <v>15.61741691201373</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08816157152327583</v>
+        <v>0.08806629290463934</v>
       </c>
       <c r="C11">
-        <v>6429.394575011484</v>
+        <v>6371.335656017117</v>
       </c>
       <c r="D11">
-        <v>6319.110575011485</v>
+        <v>6330.075656017117</v>
       </c>
       <c r="E11">
-        <v>-4235.884</v>
+        <v>-4166.860000000001</v>
       </c>
       <c r="F11">
-        <v>621.216</v>
+        <v>690.24</v>
       </c>
       <c r="G11">
         <v>731.5</v>
@@ -2189,28 +2189,28 @@
         <v>488</v>
       </c>
       <c r="M11">
-        <v>31.2471648</v>
+        <v>34.719072</v>
       </c>
       <c r="N11">
-        <v>456.7528352</v>
+        <v>453.280928</v>
       </c>
       <c r="O11">
-        <v>68.51292527999999</v>
+        <v>67.9921392</v>
       </c>
       <c r="P11">
-        <v>388.23990992</v>
+        <v>385.2887888</v>
       </c>
       <c r="Q11">
-        <v>704.2399099199999</v>
+        <v>701.2887888</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09265233134425915</v>
+        <v>0.09310088100515482</v>
       </c>
       <c r="T11">
-        <v>0.8887714125930606</v>
+        <v>0.8972802339108971</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.61741691201373</v>
+        <v>14.05567522081236</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08806629290463934</v>
+        <v>0.08811126428600283</v>
       </c>
       <c r="C12">
-        <v>6371.335656017117</v>
+        <v>6297.131414433205</v>
       </c>
       <c r="D12">
-        <v>6330.075656017117</v>
+        <v>6324.895414433206</v>
       </c>
       <c r="E12">
-        <v>-4166.860000000001</v>
+        <v>-4097.836</v>
       </c>
       <c r="F12">
-        <v>690.2400000000001</v>
+        <v>759.264</v>
       </c>
       <c r="G12">
         <v>731.5</v>
@@ -2271,45 +2271,45 @@
         <v>488</v>
       </c>
       <c r="M12">
-        <v>34.719072</v>
+        <v>39.3298752</v>
       </c>
       <c r="N12">
-        <v>453.280928</v>
+        <v>448.6701248</v>
       </c>
       <c r="O12">
-        <v>67.9921392</v>
+        <v>67.30051872</v>
       </c>
       <c r="P12">
-        <v>385.2887888</v>
+        <v>381.36960608</v>
       </c>
       <c r="Q12">
-        <v>701.2887888</v>
+        <v>697.36960608</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09310088100515482</v>
+        <v>0.09355951043371105</v>
       </c>
       <c r="T12">
-        <v>0.8972802339108971</v>
+        <v>0.9059802646965499</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.15</v>
       </c>
       <c r="W12">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>14.05567522081235</v>
+        <v>12.40787054417096</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08811126428600283</v>
+        <v>0.08802873566736634</v>
       </c>
       <c r="C13">
-        <v>6297.131414433205</v>
+        <v>6237.620371126481</v>
       </c>
       <c r="D13">
-        <v>6324.895414433206</v>
+        <v>6334.408371126481</v>
       </c>
       <c r="E13">
-        <v>-4097.836</v>
+        <v>-4028.812</v>
       </c>
       <c r="F13">
-        <v>759.264</v>
+        <v>828.288</v>
       </c>
       <c r="G13">
         <v>731.5</v>
@@ -2353,28 +2353,28 @@
         <v>488</v>
       </c>
       <c r="M13">
-        <v>39.3298752</v>
+        <v>42.9053184</v>
       </c>
       <c r="N13">
-        <v>448.6701248</v>
+        <v>445.0946816</v>
       </c>
       <c r="O13">
-        <v>67.30051872</v>
+        <v>66.76420224</v>
       </c>
       <c r="P13">
-        <v>381.36960608</v>
+        <v>378.33047936</v>
       </c>
       <c r="Q13">
-        <v>697.36960608</v>
+        <v>694.33047936</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09355951043371105</v>
+        <v>0.09402856325837083</v>
       </c>
       <c r="T13">
-        <v>0.9059802646965499</v>
+        <v>0.9148780234546041</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.40787054417096</v>
+        <v>11.37388133215672</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08802873566736634</v>
+        <v>0.08794620704872982</v>
       </c>
       <c r="C14">
-        <v>6237.620371126481</v>
+        <v>6178.137986842599</v>
       </c>
       <c r="D14">
-        <v>6334.408371126481</v>
+        <v>6343.949986842599</v>
       </c>
       <c r="E14">
-        <v>-4028.812</v>
+        <v>-3959.788</v>
       </c>
       <c r="F14">
-        <v>828.288</v>
+        <v>897.3120000000001</v>
       </c>
       <c r="G14">
         <v>731.5</v>
@@ -2435,28 +2435,28 @@
         <v>488</v>
       </c>
       <c r="M14">
-        <v>42.9053184</v>
+        <v>46.48076160000001</v>
       </c>
       <c r="N14">
-        <v>445.0946816</v>
+        <v>441.5192384</v>
       </c>
       <c r="O14">
-        <v>66.76420224</v>
+        <v>66.22788575999999</v>
       </c>
       <c r="P14">
-        <v>378.33047936</v>
+        <v>375.29135264</v>
       </c>
       <c r="Q14">
-        <v>694.33047936</v>
+        <v>691.29135264</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09402856325837083</v>
+        <v>0.09450839890658599</v>
       </c>
       <c r="T14">
-        <v>0.9148780234546041</v>
+        <v>0.9239803283910042</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.37388133215672</v>
+        <v>10.49896738352927</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08794620704872982</v>
+        <v>0.0880659784300933</v>
       </c>
       <c r="C15">
-        <v>6178.137986842599</v>
+        <v>6095.275910133474</v>
       </c>
       <c r="D15">
-        <v>6343.949986842599</v>
+        <v>6330.111910133474</v>
       </c>
       <c r="E15">
-        <v>-3959.788</v>
+        <v>-3890.764</v>
       </c>
       <c r="F15">
-        <v>897.3120000000001</v>
+        <v>966.3360000000001</v>
       </c>
       <c r="G15">
         <v>731.5</v>
@@ -2517,45 +2517,45 @@
         <v>488</v>
       </c>
       <c r="M15">
-        <v>46.48076160000001</v>
+        <v>51.69897600000001</v>
       </c>
       <c r="N15">
-        <v>441.5192384</v>
+        <v>436.301024</v>
       </c>
       <c r="O15">
-        <v>66.22788575999999</v>
+        <v>65.4451536</v>
       </c>
       <c r="P15">
-        <v>375.29135264</v>
+        <v>370.8558704</v>
       </c>
       <c r="Q15">
-        <v>691.29135264</v>
+        <v>686.8558704</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09450839890658599</v>
+        <v>0.09499939352336431</v>
       </c>
       <c r="T15">
-        <v>0.9239803283910042</v>
+        <v>0.9332943148375532</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.15</v>
       </c>
       <c r="W15">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>10.49896738352927</v>
+        <v>9.439258526126318</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0880659784300933</v>
+        <v>0.0879978998114568</v>
       </c>
       <c r="C16">
-        <v>6095.275910133474</v>
+        <v>6034.110124057905</v>
       </c>
       <c r="D16">
-        <v>6330.111910133474</v>
+        <v>6337.970124057904</v>
       </c>
       <c r="E16">
-        <v>-3890.764</v>
+        <v>-3821.74</v>
       </c>
       <c r="F16">
-        <v>966.3360000000001</v>
+        <v>1035.36</v>
       </c>
       <c r="G16">
         <v>731.5</v>
@@ -2599,28 +2599,28 @@
         <v>488</v>
       </c>
       <c r="M16">
-        <v>51.69897600000001</v>
+        <v>55.39176</v>
       </c>
       <c r="N16">
-        <v>436.301024</v>
+        <v>432.60824</v>
       </c>
       <c r="O16">
-        <v>65.4451536</v>
+        <v>64.89123600000001</v>
       </c>
       <c r="P16">
-        <v>370.8558704</v>
+        <v>367.717004</v>
       </c>
       <c r="Q16">
-        <v>686.8558704</v>
+        <v>683.7170040000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09499939352336431</v>
+        <v>0.09550194095465506</v>
       </c>
       <c r="T16">
-        <v>0.9332943148375532</v>
+        <v>0.9428274539063739</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.439258526126318</v>
+        <v>8.809974624384566</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0879978998114568</v>
+        <v>0.08792982119282029</v>
       </c>
       <c r="C17">
-        <v>6034.110124057905</v>
+        <v>5972.963872638503</v>
       </c>
       <c r="D17">
-        <v>6337.970124057904</v>
+        <v>6345.847872638503</v>
       </c>
       <c r="E17">
-        <v>-3821.74</v>
+        <v>-3752.716</v>
       </c>
       <c r="F17">
-        <v>1035.36</v>
+        <v>1104.384</v>
       </c>
       <c r="G17">
         <v>731.5</v>
@@ -2681,28 +2681,28 @@
         <v>488</v>
       </c>
       <c r="M17">
-        <v>55.39176</v>
+        <v>59.084544</v>
       </c>
       <c r="N17">
-        <v>432.60824</v>
+        <v>428.915456</v>
       </c>
       <c r="O17">
-        <v>64.89123600000001</v>
+        <v>64.3373184</v>
       </c>
       <c r="P17">
-        <v>367.717004</v>
+        <v>364.5781376</v>
       </c>
       <c r="Q17">
-        <v>683.7170040000001</v>
+        <v>680.5781376</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09550194095465506</v>
+        <v>0.09601645380097654</v>
       </c>
       <c r="T17">
-        <v>0.9428274539063739</v>
+        <v>0.9525875724768335</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.809974624384566</v>
+        <v>8.259351210360531</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08792982119282029</v>
+        <v>0.08786174257418378</v>
       </c>
       <c r="C18">
-        <v>5972.963872638503</v>
+        <v>5911.837228807433</v>
       </c>
       <c r="D18">
-        <v>6345.847872638503</v>
+        <v>6353.745228807434</v>
       </c>
       <c r="E18">
-        <v>-3752.716</v>
+        <v>-3683.692</v>
       </c>
       <c r="F18">
-        <v>1104.384</v>
+        <v>1173.408</v>
       </c>
       <c r="G18">
         <v>731.5</v>
@@ -2763,28 +2763,28 @@
         <v>488</v>
       </c>
       <c r="M18">
-        <v>59.084544</v>
+        <v>62.777328</v>
       </c>
       <c r="N18">
-        <v>428.915456</v>
+        <v>425.222672</v>
       </c>
       <c r="O18">
-        <v>64.3373184</v>
+        <v>63.7834008</v>
       </c>
       <c r="P18">
-        <v>364.5781376</v>
+        <v>361.4392712</v>
       </c>
       <c r="Q18">
-        <v>680.5781376</v>
+        <v>677.4392712</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09601645380097654</v>
+        <v>0.09654336454720938</v>
       </c>
       <c r="T18">
-        <v>0.9525875724768335</v>
+        <v>0.9625828746273039</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.259351210360531</v>
+        <v>7.773507021515792</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08786174257418378</v>
+        <v>0.08791606395554727</v>
       </c>
       <c r="C19">
-        <v>5911.837228807433</v>
+        <v>5836.510176780459</v>
       </c>
       <c r="D19">
-        <v>6353.745228807434</v>
+        <v>6347.442176780459</v>
       </c>
       <c r="E19">
-        <v>-3683.692</v>
+        <v>-3614.668</v>
       </c>
       <c r="F19">
-        <v>1173.408</v>
+        <v>1242.432</v>
       </c>
       <c r="G19">
         <v>731.5</v>
@@ -2845,45 +2845,45 @@
         <v>488</v>
       </c>
       <c r="M19">
-        <v>62.777328</v>
+        <v>67.46405760000002</v>
       </c>
       <c r="N19">
-        <v>425.222672</v>
+        <v>420.5359424</v>
       </c>
       <c r="O19">
-        <v>63.7834008</v>
+        <v>63.08039135999999</v>
       </c>
       <c r="P19">
-        <v>361.4392712</v>
+        <v>357.4555510399999</v>
       </c>
       <c r="Q19">
-        <v>677.4392712</v>
+        <v>673.4555510399999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09654336454720938</v>
+        <v>0.09708312677505765</v>
       </c>
       <c r="T19">
-        <v>0.9625828746273039</v>
+        <v>0.9728219646351027</v>
       </c>
       <c r="U19">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.15</v>
       </c>
       <c r="W19">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>7.773507021515792</v>
+        <v>7.233481313759578</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08791606395554727</v>
+        <v>0.08785478533691078</v>
       </c>
       <c r="C20">
-        <v>5836.510176780459</v>
+        <v>5774.597399657739</v>
       </c>
       <c r="D20">
-        <v>6347.442176780459</v>
+        <v>6354.553399657739</v>
       </c>
       <c r="E20">
-        <v>-3614.668000000001</v>
+        <v>-3545.644</v>
       </c>
       <c r="F20">
-        <v>1242.432</v>
+        <v>1311.456</v>
       </c>
       <c r="G20">
         <v>731.5</v>
@@ -2927,28 +2927,28 @@
         <v>488</v>
       </c>
       <c r="M20">
-        <v>67.4640576</v>
+        <v>71.2120608</v>
       </c>
       <c r="N20">
-        <v>420.5359424</v>
+        <v>416.7879392</v>
       </c>
       <c r="O20">
-        <v>63.08039136</v>
+        <v>62.51819087999999</v>
       </c>
       <c r="P20">
-        <v>357.45555104</v>
+        <v>354.26974832</v>
       </c>
       <c r="Q20">
-        <v>673.45555104</v>
+        <v>670.26974832</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09708312677505765</v>
+        <v>0.09763621646532195</v>
       </c>
       <c r="T20">
-        <v>0.9728219646351027</v>
+        <v>0.9833138716801313</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.23348131375958</v>
+        <v>6.852771770930128</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08785478533691078</v>
+        <v>0.08779350671827428</v>
       </c>
       <c r="C21">
-        <v>5774.597399657739</v>
+        <v>5712.700574223087</v>
       </c>
       <c r="D21">
-        <v>6354.553399657739</v>
+        <v>6361.680574223087</v>
       </c>
       <c r="E21">
-        <v>-3545.644</v>
+        <v>-3476.62</v>
       </c>
       <c r="F21">
-        <v>1311.456</v>
+        <v>1380.48</v>
       </c>
       <c r="G21">
         <v>731.5</v>
@@ -3009,28 +3009,28 @@
         <v>488</v>
       </c>
       <c r="M21">
-        <v>71.2120608</v>
+        <v>74.96006400000002</v>
       </c>
       <c r="N21">
-        <v>416.7879392</v>
+        <v>413.039936</v>
       </c>
       <c r="O21">
-        <v>62.51819087999999</v>
+        <v>61.9559904</v>
       </c>
       <c r="P21">
-        <v>354.26974832</v>
+        <v>351.0839456</v>
       </c>
       <c r="Q21">
-        <v>670.26974832</v>
+        <v>667.0839456</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09763621646532195</v>
+        <v>0.09820313339784284</v>
       </c>
       <c r="T21">
-        <v>0.9833138716801313</v>
+        <v>0.9940680764012856</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.852771770930128</v>
+        <v>6.510133182383621</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08779350671827428</v>
+        <v>0.08773222809963777</v>
       </c>
       <c r="C22">
-        <v>5712.700574223087</v>
+        <v>5650.819754210315</v>
       </c>
       <c r="D22">
-        <v>6361.680574223087</v>
+        <v>6368.823754210316</v>
       </c>
       <c r="E22">
-        <v>-3476.62</v>
+        <v>-3407.596</v>
       </c>
       <c r="F22">
-        <v>1380.48</v>
+        <v>1449.504</v>
       </c>
       <c r="G22">
         <v>731.5</v>
@@ -3091,28 +3091,28 @@
         <v>488</v>
       </c>
       <c r="M22">
-        <v>74.96006400000002</v>
+        <v>78.70806720000002</v>
       </c>
       <c r="N22">
-        <v>413.039936</v>
+        <v>409.2919328</v>
       </c>
       <c r="O22">
-        <v>61.9559904</v>
+        <v>61.39378992</v>
       </c>
       <c r="P22">
-        <v>351.0839456</v>
+        <v>347.89814288</v>
       </c>
       <c r="Q22">
-        <v>667.0839456</v>
+        <v>663.89814288</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09820313339784284</v>
+        <v>0.09878440265776932</v>
       </c>
       <c r="T22">
-        <v>0.9940680764012856</v>
+        <v>1.005094539469811</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.510133182383621</v>
+        <v>6.200126840365353</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08773222809963775</v>
+        <v>0.08785794948100126</v>
       </c>
       <c r="C23">
-        <v>5650.819754210318</v>
+        <v>5567.157818929574</v>
       </c>
       <c r="D23">
-        <v>6368.823754210318</v>
+        <v>6354.185818929574</v>
       </c>
       <c r="E23">
-        <v>-3407.596</v>
+        <v>-3338.572</v>
       </c>
       <c r="F23">
-        <v>1449.504</v>
+        <v>1518.528</v>
       </c>
       <c r="G23">
         <v>731.5</v>
@@ -3173,45 +3173,45 @@
         <v>488</v>
       </c>
       <c r="M23">
-        <v>78.7080672</v>
+        <v>83.9745984</v>
       </c>
       <c r="N23">
-        <v>409.2919328</v>
+        <v>404.0254016</v>
       </c>
       <c r="O23">
-        <v>61.39378992</v>
+        <v>60.60381024</v>
       </c>
       <c r="P23">
-        <v>347.89814288</v>
+        <v>343.42159136</v>
       </c>
       <c r="Q23">
-        <v>663.89814288</v>
+        <v>659.42159136</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0987844026577693</v>
+        <v>0.09938057625769392</v>
       </c>
       <c r="T23">
-        <v>1.005094539469811</v>
+        <v>1.016403732360606</v>
       </c>
       <c r="U23">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V23">
         <v>0.15</v>
       </c>
       <c r="W23">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.200126840365354</v>
+        <v>5.81128114094083</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08785794948100126</v>
+        <v>0.08780517086236475</v>
       </c>
       <c r="C24">
-        <v>5567.157818929574</v>
+        <v>5504.270712883796</v>
       </c>
       <c r="D24">
-        <v>6354.185818929574</v>
+        <v>6360.322712883795</v>
       </c>
       <c r="E24">
-        <v>-3338.572</v>
+        <v>-3269.548</v>
       </c>
       <c r="F24">
-        <v>1518.528</v>
+        <v>1587.552</v>
       </c>
       <c r="G24">
         <v>731.5</v>
@@ -3255,28 +3255,28 @@
         <v>488</v>
       </c>
       <c r="M24">
-        <v>83.9745984</v>
+        <v>87.79162560000002</v>
       </c>
       <c r="N24">
-        <v>404.0254016</v>
+        <v>400.2083744</v>
       </c>
       <c r="O24">
-        <v>60.60381024</v>
+        <v>60.03125615999999</v>
       </c>
       <c r="P24">
-        <v>343.42159136</v>
+        <v>340.17711824</v>
       </c>
       <c r="Q24">
-        <v>659.42159136</v>
+        <v>656.17711824</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09938057625769392</v>
+        <v>0.09999223488618798</v>
       </c>
       <c r="T24">
-        <v>1.016403732360606</v>
+        <v>1.028006670521292</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.81128114094083</v>
+        <v>5.558616743508619</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08780517086236475</v>
+        <v>0.08775239224372824</v>
       </c>
       <c r="C25">
-        <v>5504.270712883796</v>
+        <v>5441.395472363266</v>
       </c>
       <c r="D25">
-        <v>6360.322712883795</v>
+        <v>6366.471472363266</v>
       </c>
       <c r="E25">
-        <v>-3269.548</v>
+        <v>-3200.524</v>
       </c>
       <c r="F25">
-        <v>1587.552</v>
+        <v>1656.576</v>
       </c>
       <c r="G25">
         <v>731.5</v>
@@ -3337,28 +3337,28 @@
         <v>488</v>
       </c>
       <c r="M25">
-        <v>87.79162560000002</v>
+        <v>91.60865280000002</v>
       </c>
       <c r="N25">
-        <v>400.2083744</v>
+        <v>396.3913472</v>
       </c>
       <c r="O25">
-        <v>60.03125615999999</v>
+        <v>59.45870207999999</v>
       </c>
       <c r="P25">
-        <v>340.17711824</v>
+        <v>336.93264512</v>
       </c>
       <c r="Q25">
-        <v>656.17711824</v>
+        <v>652.93264512</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09999223488618798</v>
+        <v>0.1006199897943793</v>
       </c>
       <c r="T25">
-        <v>1.028006670521292</v>
+        <v>1.039914949159891</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.558616743508619</v>
+        <v>5.327007712529094</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08775239224372824</v>
+        <v>0.08769961362509175</v>
       </c>
       <c r="C26">
-        <v>5441.395472363266</v>
+        <v>5378.532131813813</v>
       </c>
       <c r="D26">
-        <v>6366.471472363266</v>
+        <v>6372.632131813813</v>
       </c>
       <c r="E26">
-        <v>-3200.524</v>
+        <v>-3131.5</v>
       </c>
       <c r="F26">
-        <v>1656.576</v>
+        <v>1725.6</v>
       </c>
       <c r="G26">
         <v>731.5</v>
@@ -3419,28 +3419,28 @@
         <v>488</v>
       </c>
       <c r="M26">
-        <v>91.6086528</v>
+        <v>95.42568000000001</v>
       </c>
       <c r="N26">
-        <v>396.3913472</v>
+        <v>392.57432</v>
       </c>
       <c r="O26">
-        <v>59.45870207999999</v>
+        <v>58.886148</v>
       </c>
       <c r="P26">
-        <v>336.93264512</v>
+        <v>333.688172</v>
       </c>
       <c r="Q26">
-        <v>652.93264512</v>
+        <v>649.688172</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1006199897943793</v>
+        <v>0.1012644848334557</v>
       </c>
       <c r="T26">
-        <v>1.039914949159891</v>
+        <v>1.052140781895519</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.327007712529094</v>
+        <v>5.11392740402793</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08769961362509175</v>
+        <v>0.08764683500645523</v>
       </c>
       <c r="C27">
-        <v>5378.532131813813</v>
+        <v>5315.680725814729</v>
       </c>
       <c r="D27">
-        <v>6372.632131813813</v>
+        <v>6378.804725814729</v>
       </c>
       <c r="E27">
-        <v>-3131.5</v>
+        <v>-3062.476</v>
       </c>
       <c r="F27">
-        <v>1725.6</v>
+        <v>1794.624</v>
       </c>
       <c r="G27">
         <v>731.5</v>
@@ -3501,28 +3501,28 @@
         <v>488</v>
       </c>
       <c r="M27">
-        <v>95.42568000000001</v>
+        <v>99.24270720000001</v>
       </c>
       <c r="N27">
-        <v>392.57432</v>
+        <v>388.7572928</v>
       </c>
       <c r="O27">
-        <v>58.886148</v>
+        <v>58.31359391999999</v>
       </c>
       <c r="P27">
-        <v>333.688172</v>
+        <v>330.4436988799999</v>
       </c>
       <c r="Q27">
-        <v>649.688172</v>
+        <v>646.4436988799999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1012644848334557</v>
+        <v>0.1019263986573719</v>
       </c>
       <c r="T27">
-        <v>1.052140781895519</v>
+        <v>1.064697042542921</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.11392740402793</v>
+        <v>4.917237888488394</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08764683500645523</v>
+        <v>0.08759405638781873</v>
       </c>
       <c r="C28">
-        <v>5315.680725814729</v>
+        <v>5252.841289079397</v>
       </c>
       <c r="D28">
-        <v>6378.804725814729</v>
+        <v>6384.989289079397</v>
       </c>
       <c r="E28">
-        <v>-3062.476</v>
+        <v>-2993.452</v>
       </c>
       <c r="F28">
-        <v>1794.624</v>
+        <v>1863.648</v>
       </c>
       <c r="G28">
         <v>731.5</v>
@@ -3583,28 +3583,28 @@
         <v>488</v>
       </c>
       <c r="M28">
-        <v>99.24270720000001</v>
+        <v>103.0597344</v>
       </c>
       <c r="N28">
-        <v>388.7572928</v>
+        <v>384.9402656</v>
       </c>
       <c r="O28">
-        <v>58.31359391999999</v>
+        <v>57.74103983999999</v>
       </c>
       <c r="P28">
-        <v>330.4436988799999</v>
+        <v>327.19922576</v>
       </c>
       <c r="Q28">
-        <v>646.4436988799999</v>
+        <v>643.19922576</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1019263986573719</v>
+        <v>0.102606447106601</v>
       </c>
       <c r="T28">
-        <v>1.064697042542921</v>
+        <v>1.077597310331347</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.917237888488394</v>
+        <v>4.735117966692528</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08759405638781873</v>
+        <v>0.08754127776918222</v>
       </c>
       <c r="C29">
-        <v>5252.841289079397</v>
+        <v>5190.013856455969</v>
       </c>
       <c r="D29">
-        <v>6384.989289079397</v>
+        <v>6391.18585645597</v>
       </c>
       <c r="E29">
-        <v>-2993.452</v>
+        <v>-2924.428</v>
       </c>
       <c r="F29">
-        <v>1863.648</v>
+        <v>1932.672</v>
       </c>
       <c r="G29">
         <v>731.5</v>
@@ -3665,28 +3665,28 @@
         <v>488</v>
       </c>
       <c r="M29">
-        <v>103.0597344</v>
+        <v>106.8767616</v>
       </c>
       <c r="N29">
-        <v>384.9402656</v>
+        <v>381.1232384</v>
       </c>
       <c r="O29">
-        <v>57.74103983999999</v>
+        <v>57.16848576</v>
       </c>
       <c r="P29">
-        <v>327.19922576</v>
+        <v>323.95475264</v>
       </c>
       <c r="Q29">
-        <v>643.19922576</v>
+        <v>639.9547526399999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.102606447106601</v>
+        <v>0.1033053857905309</v>
       </c>
       <c r="T29">
-        <v>1.077597310331347</v>
+        <v>1.090855918891674</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.735117966692528</v>
+        <v>4.566006610739223</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08754127776918222</v>
+        <v>0.08810474915054571</v>
       </c>
       <c r="C30">
-        <v>5190.013856455969</v>
+        <v>5055.449365928614</v>
       </c>
       <c r="D30">
-        <v>6391.18585645597</v>
+        <v>6325.645365928615</v>
       </c>
       <c r="E30">
-        <v>-2924.428</v>
+        <v>-2855.404</v>
       </c>
       <c r="F30">
-        <v>1932.672</v>
+        <v>2001.696</v>
       </c>
       <c r="G30">
         <v>731.5</v>
@@ -3747,45 +3747,45 @@
         <v>488</v>
       </c>
       <c r="M30">
-        <v>106.8767616</v>
+        <v>115.6980288</v>
       </c>
       <c r="N30">
-        <v>381.1232384</v>
+        <v>372.3019712</v>
       </c>
       <c r="O30">
-        <v>57.16848576</v>
+        <v>55.84529567999999</v>
       </c>
       <c r="P30">
-        <v>323.95475264</v>
+        <v>316.45667552</v>
       </c>
       <c r="Q30">
-        <v>639.9547526399999</v>
+        <v>632.45667552</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1033053857905309</v>
+        <v>0.1040240128880926</v>
       </c>
       <c r="T30">
-        <v>1.090855918891674</v>
+        <v>1.104488009383279</v>
       </c>
       <c r="U30">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V30">
         <v>0.15</v>
       </c>
       <c r="W30">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.566006610739223</v>
+        <v>4.21787652790157</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08810474915054571</v>
+        <v>0.0880732205319092</v>
       </c>
       <c r="C31">
-        <v>5055.449365928615</v>
+        <v>4990.057111630541</v>
       </c>
       <c r="D31">
-        <v>6325.645365928615</v>
+        <v>6329.277111630541</v>
       </c>
       <c r="E31">
-        <v>-2855.404</v>
+        <v>-2786.38</v>
       </c>
       <c r="F31">
-        <v>2001.696</v>
+        <v>2070.72</v>
       </c>
       <c r="G31">
         <v>731.5</v>
@@ -3829,28 +3829,28 @@
         <v>488</v>
       </c>
       <c r="M31">
-        <v>115.6980288</v>
+        <v>119.687616</v>
       </c>
       <c r="N31">
-        <v>372.3019712</v>
+        <v>368.312384</v>
       </c>
       <c r="O31">
-        <v>55.84529568</v>
+        <v>55.24685759999999</v>
       </c>
       <c r="P31">
-        <v>316.45667552</v>
+        <v>313.0655264</v>
       </c>
       <c r="Q31">
-        <v>632.4566755200001</v>
+        <v>629.0655264</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1040240128880926</v>
+        <v>0.1047631721884417</v>
       </c>
       <c r="T31">
-        <v>1.104488009383279</v>
+        <v>1.118509588174643</v>
       </c>
       <c r="U31">
         <v>0.0578</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.217876527901572</v>
+        <v>4.077280643638185</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0880732205319092</v>
+        <v>0.0889639419132727</v>
       </c>
       <c r="C32">
-        <v>4990.057111630541</v>
+        <v>4820.011579571483</v>
       </c>
       <c r="D32">
-        <v>6329.277111630541</v>
+        <v>6228.255579571483</v>
       </c>
       <c r="E32">
-        <v>-2786.38</v>
+        <v>-2717.356</v>
       </c>
       <c r="F32">
-        <v>2070.72</v>
+        <v>2139.744</v>
       </c>
       <c r="G32">
         <v>731.5</v>
@@ -3911,45 +3911,45 @@
         <v>488</v>
       </c>
       <c r="M32">
-        <v>119.687616</v>
+        <v>131.1663072</v>
       </c>
       <c r="N32">
-        <v>368.312384</v>
+        <v>356.8336928</v>
       </c>
       <c r="O32">
-        <v>55.24685759999999</v>
+        <v>53.52505392</v>
       </c>
       <c r="P32">
-        <v>313.0655264</v>
+        <v>303.30863888</v>
       </c>
       <c r="Q32">
-        <v>629.0655264</v>
+        <v>619.30863888</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1047631721884417</v>
+        <v>0.1055237563960474</v>
       </c>
       <c r="T32">
-        <v>1.118509588174643</v>
+        <v>1.132937589539669</v>
       </c>
       <c r="U32">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V32">
         <v>0.15</v>
       </c>
       <c r="W32">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.077280643638185</v>
+        <v>3.720467629357793</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0889639419132727</v>
+        <v>0.08896216329463617</v>
       </c>
       <c r="C33">
-        <v>4820.011579571483</v>
+        <v>4751.186088967796</v>
       </c>
       <c r="D33">
-        <v>6228.255579571483</v>
+        <v>6228.454088967796</v>
       </c>
       <c r="E33">
-        <v>-2717.356</v>
+        <v>-2648.332</v>
       </c>
       <c r="F33">
-        <v>2139.744</v>
+        <v>2208.768</v>
       </c>
       <c r="G33">
         <v>731.5</v>
@@ -3993,28 +3993,28 @@
         <v>488</v>
       </c>
       <c r="M33">
-        <v>131.1663072</v>
+        <v>135.3974784</v>
       </c>
       <c r="N33">
-        <v>356.8336928</v>
+        <v>352.6025216</v>
       </c>
       <c r="O33">
-        <v>53.52505392</v>
+        <v>52.89037824</v>
       </c>
       <c r="P33">
-        <v>303.30863888</v>
+        <v>299.71214336</v>
       </c>
       <c r="Q33">
-        <v>619.30863888</v>
+        <v>615.71214336</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1055237563960474</v>
+        <v>0.1063067107274062</v>
       </c>
       <c r="T33">
-        <v>1.132937589539669</v>
+        <v>1.14778994388602</v>
       </c>
       <c r="U33">
         <v>0.0613</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.720467629357793</v>
+        <v>3.604203015940362</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08896216329463617</v>
+        <v>0.08974578467599968</v>
       </c>
       <c r="C34">
-        <v>4751.186088967796</v>
+        <v>4595.911458200035</v>
       </c>
       <c r="D34">
-        <v>6228.454088967796</v>
+        <v>6142.203458200035</v>
       </c>
       <c r="E34">
-        <v>-2648.332</v>
+        <v>-2579.308</v>
       </c>
       <c r="F34">
-        <v>2208.768</v>
+        <v>2277.792</v>
       </c>
       <c r="G34">
         <v>731.5</v>
@@ -4075,45 +4075,45 @@
         <v>488</v>
       </c>
       <c r="M34">
-        <v>135.3974784</v>
+        <v>146.0064672</v>
       </c>
       <c r="N34">
-        <v>352.6025216</v>
+        <v>341.9935328</v>
       </c>
       <c r="O34">
-        <v>52.89037824</v>
+        <v>51.29902992</v>
       </c>
       <c r="P34">
-        <v>299.71214336</v>
+        <v>290.69450288</v>
       </c>
       <c r="Q34">
-        <v>615.71214336</v>
+        <v>606.69450288</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1063067107274062</v>
+        <v>0.1071130368298503</v>
       </c>
       <c r="T34">
-        <v>1.14778994388602</v>
+        <v>1.163085652093457</v>
       </c>
       <c r="U34">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V34">
         <v>0.15</v>
       </c>
       <c r="W34">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>3.604203015940362</v>
+        <v>3.342317702485989</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08974578467599968</v>
+        <v>0.08976780605736318</v>
       </c>
       <c r="C35">
-        <v>4595.911458200035</v>
+        <v>4524.498131605353</v>
       </c>
       <c r="D35">
-        <v>6142.203458200035</v>
+        <v>6139.814131605352</v>
       </c>
       <c r="E35">
-        <v>-2579.308</v>
+        <v>-2510.284</v>
       </c>
       <c r="F35">
-        <v>2277.792</v>
+        <v>2346.816</v>
       </c>
       <c r="G35">
         <v>731.5</v>
@@ -4157,28 +4157,28 @@
         <v>488</v>
       </c>
       <c r="M35">
-        <v>146.0064672</v>
+        <v>150.4309056</v>
       </c>
       <c r="N35">
-        <v>341.9935328</v>
+        <v>337.5690944</v>
       </c>
       <c r="O35">
-        <v>51.29902992</v>
+        <v>50.63536415999999</v>
       </c>
       <c r="P35">
-        <v>290.69450288</v>
+        <v>286.93373024</v>
       </c>
       <c r="Q35">
-        <v>606.69450288</v>
+        <v>602.9337302399999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1071130368298503</v>
+        <v>0.1079437970566109</v>
       </c>
       <c r="T35">
-        <v>1.163085652093457</v>
+        <v>1.17884486661021</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.342317702485989</v>
+        <v>3.244014240648166</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08976780605736318</v>
+        <v>0.08978982743872665</v>
       </c>
       <c r="C36">
-        <v>4524.498131605353</v>
+        <v>4453.086663191278</v>
       </c>
       <c r="D36">
-        <v>6139.814131605352</v>
+        <v>6137.426663191279</v>
       </c>
       <c r="E36">
-        <v>-2510.284</v>
+        <v>-2441.26</v>
       </c>
       <c r="F36">
-        <v>2346.816</v>
+        <v>2415.840000000001</v>
       </c>
       <c r="G36">
         <v>731.5</v>
@@ -4239,28 +4239,28 @@
         <v>488</v>
       </c>
       <c r="M36">
-        <v>150.4309056</v>
+        <v>154.8553440000001</v>
       </c>
       <c r="N36">
-        <v>337.5690944</v>
+        <v>333.1446559999999</v>
       </c>
       <c r="O36">
-        <v>50.63536415999999</v>
+        <v>49.97169839999999</v>
       </c>
       <c r="P36">
-        <v>286.93373024</v>
+        <v>283.1729576</v>
       </c>
       <c r="Q36">
-        <v>602.9337302399999</v>
+        <v>599.1729576</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1079437970566109</v>
+        <v>0.1088001191365026</v>
       </c>
       <c r="T36">
-        <v>1.17884486661021</v>
+        <v>1.19508898003517</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.244014240648166</v>
+        <v>3.151328119486789</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08978982743872665</v>
+        <v>0.08981184882009016</v>
       </c>
       <c r="C37">
-        <v>4453.086663191278</v>
+        <v>4381.677050790989</v>
       </c>
       <c r="D37">
-        <v>6137.426663191279</v>
+        <v>6135.041050790989</v>
       </c>
       <c r="E37">
-        <v>-2441.26</v>
+        <v>-2372.236</v>
       </c>
       <c r="F37">
-        <v>2415.840000000001</v>
+        <v>2484.864</v>
       </c>
       <c r="G37">
         <v>731.5</v>
@@ -4321,28 +4321,28 @@
         <v>488</v>
       </c>
       <c r="M37">
-        <v>154.8553440000001</v>
+        <v>159.2797824</v>
       </c>
       <c r="N37">
-        <v>333.1446559999999</v>
+        <v>328.7202176</v>
       </c>
       <c r="O37">
-        <v>49.97169839999999</v>
+        <v>49.30803263999999</v>
       </c>
       <c r="P37">
-        <v>283.1729576</v>
+        <v>279.41218496</v>
       </c>
       <c r="Q37">
-        <v>599.1729576</v>
+        <v>595.41218496</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1088001191365026</v>
+        <v>0.1096832012813909</v>
       </c>
       <c r="T37">
-        <v>1.19508898003517</v>
+        <v>1.21184072200466</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.151328119486789</v>
+        <v>3.063791227278823</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08981184882009016</v>
+        <v>0.09228697020145368</v>
       </c>
       <c r="C38">
-        <v>4381.67705079099</v>
+        <v>4055.842918603121</v>
       </c>
       <c r="D38">
-        <v>6135.041050790989</v>
+        <v>5878.230918603122</v>
       </c>
       <c r="E38">
-        <v>-2372.236</v>
+        <v>-2303.212</v>
       </c>
       <c r="F38">
-        <v>2484.864</v>
+        <v>2553.888</v>
       </c>
       <c r="G38">
         <v>731.5</v>
@@ -4403,45 +4403,45 @@
         <v>488</v>
       </c>
       <c r="M38">
-        <v>159.2797824</v>
+        <v>183.6245472000001</v>
       </c>
       <c r="N38">
-        <v>328.7202176</v>
+        <v>304.3754527999999</v>
       </c>
       <c r="O38">
-        <v>49.30803263999999</v>
+        <v>45.65631791999999</v>
       </c>
       <c r="P38">
-        <v>279.41218496</v>
+        <v>258.71913488</v>
       </c>
       <c r="Q38">
-        <v>595.41218496</v>
+        <v>574.71913488</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1096832012813909</v>
+        <v>0.1105943177800852</v>
       </c>
       <c r="T38">
-        <v>1.21184072200466</v>
+        <v>1.229124265306515</v>
       </c>
       <c r="U38">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V38">
         <v>0.15</v>
       </c>
       <c r="W38">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.063791227278823</v>
+        <v>2.657596750768189</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09228697020145368</v>
+        <v>0.09237529158281714</v>
       </c>
       <c r="C39">
-        <v>4055.842918603121</v>
+        <v>3978.051687542672</v>
       </c>
       <c r="D39">
-        <v>5878.230918603122</v>
+        <v>5869.463687542672</v>
       </c>
       <c r="E39">
-        <v>-2303.212</v>
+        <v>-2234.188</v>
       </c>
       <c r="F39">
-        <v>2553.888</v>
+        <v>2622.912</v>
       </c>
       <c r="G39">
         <v>731.5</v>
@@ -4485,28 +4485,28 @@
         <v>488</v>
       </c>
       <c r="M39">
-        <v>183.6245472000001</v>
+        <v>188.5873728</v>
       </c>
       <c r="N39">
-        <v>304.3754527999999</v>
+        <v>299.4126272</v>
       </c>
       <c r="O39">
-        <v>45.65631791999999</v>
+        <v>44.91189408</v>
       </c>
       <c r="P39">
-        <v>258.71913488</v>
+        <v>254.50073312</v>
       </c>
       <c r="Q39">
-        <v>574.71913488</v>
+        <v>570.5007331199999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1105943177800852</v>
+        <v>0.111534825133576</v>
       </c>
       <c r="T39">
-        <v>1.229124265306515</v>
+        <v>1.246965342263269</v>
       </c>
       <c r="U39">
         <v>0.07190000000000001</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.657596750768189</v>
+        <v>2.587659994169026</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09237529158281714</v>
+        <v>0.09246361296418065</v>
       </c>
       <c r="C40">
-        <v>3978.051687542672</v>
+        <v>3900.28656973672</v>
       </c>
       <c r="D40">
-        <v>5869.463687542672</v>
+        <v>5860.72256973672</v>
       </c>
       <c r="E40">
-        <v>-2234.188</v>
+        <v>-2165.164</v>
       </c>
       <c r="F40">
-        <v>2622.912</v>
+        <v>2691.936</v>
       </c>
       <c r="G40">
         <v>731.5</v>
@@ -4567,28 +4567,28 @@
         <v>488</v>
       </c>
       <c r="M40">
-        <v>188.5873728</v>
+        <v>193.5501984</v>
       </c>
       <c r="N40">
-        <v>299.4126272</v>
+        <v>294.4498016</v>
       </c>
       <c r="O40">
-        <v>44.91189408</v>
+        <v>44.16747024</v>
       </c>
       <c r="P40">
-        <v>254.50073312</v>
+        <v>250.28233136</v>
       </c>
       <c r="Q40">
-        <v>570.5007331199999</v>
+        <v>566.2823313599999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.111534825133576</v>
+        <v>0.1125061687937388</v>
       </c>
       <c r="T40">
-        <v>1.246965342263269</v>
+        <v>1.265391372562867</v>
       </c>
       <c r="U40">
         <v>0.07190000000000001</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.587659994169026</v>
+        <v>2.521309737908282</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09246361296418065</v>
+        <v>0.09387793434554415</v>
       </c>
       <c r="C41">
-        <v>3900.28656973672</v>
+        <v>3694.751926971209</v>
       </c>
       <c r="D41">
-        <v>5860.72256973672</v>
+        <v>5724.211926971209</v>
       </c>
       <c r="E41">
-        <v>-2165.164</v>
+        <v>-2096.14</v>
       </c>
       <c r="F41">
-        <v>2691.936</v>
+        <v>2760.96</v>
       </c>
       <c r="G41">
         <v>731.5</v>
@@ -4649,45 +4649,45 @@
         <v>488</v>
       </c>
       <c r="M41">
-        <v>193.5501984</v>
+        <v>209.2807680000001</v>
       </c>
       <c r="N41">
-        <v>294.4498016</v>
+        <v>278.7192319999999</v>
       </c>
       <c r="O41">
-        <v>44.16747024</v>
+        <v>41.80788479999999</v>
       </c>
       <c r="P41">
-        <v>250.28233136</v>
+        <v>236.9113471999999</v>
       </c>
       <c r="Q41">
-        <v>566.2823313599999</v>
+        <v>552.9113471999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1125061687937388</v>
+        <v>0.1135098905759069</v>
       </c>
       <c r="T41">
-        <v>1.265391372562867</v>
+        <v>1.284431603872452</v>
       </c>
       <c r="U41">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V41">
         <v>0.15</v>
       </c>
       <c r="W41">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.521309737908282</v>
+        <v>2.331795724297035</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09387793434554415</v>
+        <v>0.09399940572690763</v>
       </c>
       <c r="C42">
-        <v>3694.751926971209</v>
+        <v>3614.299433830783</v>
       </c>
       <c r="D42">
-        <v>5724.211926971209</v>
+        <v>5712.783433830783</v>
       </c>
       <c r="E42">
-        <v>-2096.14</v>
+        <v>-2027.116</v>
       </c>
       <c r="F42">
-        <v>2760.96</v>
+        <v>2829.984</v>
       </c>
       <c r="G42">
         <v>731.5</v>
@@ -4731,28 +4731,28 @@
         <v>488</v>
       </c>
       <c r="M42">
-        <v>209.2807680000001</v>
+        <v>214.5127872</v>
       </c>
       <c r="N42">
-        <v>278.7192319999999</v>
+        <v>273.4872128</v>
       </c>
       <c r="O42">
-        <v>41.80788479999999</v>
+        <v>41.02308191999999</v>
       </c>
       <c r="P42">
-        <v>236.9113471999999</v>
+        <v>232.46413088</v>
       </c>
       <c r="Q42">
-        <v>552.9113471999999</v>
+        <v>548.46413088</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1135098905759069</v>
+        <v>0.1145476368252672</v>
       </c>
       <c r="T42">
-        <v>1.284431603872452</v>
+        <v>1.304117266751853</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.331795724297035</v>
+        <v>2.274922657850767</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09399940572690763</v>
+        <v>0.09412087710827113</v>
       </c>
       <c r="C43">
-        <v>3614.299433830783</v>
+        <v>3533.892484150507</v>
       </c>
       <c r="D43">
-        <v>5712.783433830783</v>
+        <v>5701.400484150508</v>
       </c>
       <c r="E43">
-        <v>-2027.116</v>
+        <v>-1958.092</v>
       </c>
       <c r="F43">
-        <v>2829.984</v>
+        <v>2899.008000000001</v>
       </c>
       <c r="G43">
         <v>731.5</v>
@@ -4813,28 +4813,28 @@
         <v>488</v>
       </c>
       <c r="M43">
-        <v>214.5127872</v>
+        <v>219.7448064000001</v>
       </c>
       <c r="N43">
-        <v>273.4872128</v>
+        <v>268.2551935999999</v>
       </c>
       <c r="O43">
-        <v>41.02308191999999</v>
+        <v>40.23827903999999</v>
       </c>
       <c r="P43">
-        <v>232.46413088</v>
+        <v>228.0169145599999</v>
       </c>
       <c r="Q43">
-        <v>548.46413088</v>
+        <v>544.0169145599999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1145476368252672</v>
+        <v>0.1156211674280537</v>
       </c>
       <c r="T43">
-        <v>1.304117266751853</v>
+        <v>1.324481745592612</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.274922657850767</v>
+        <v>2.220757832663844</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09412087710827115</v>
+        <v>0.09424234848963461</v>
       </c>
       <c r="C44">
-        <v>3533.892484150506</v>
+        <v>3453.530806230257</v>
       </c>
       <c r="D44">
-        <v>5701.400484150507</v>
+        <v>5690.062806230258</v>
       </c>
       <c r="E44">
-        <v>-1958.092</v>
+        <v>-1889.068</v>
       </c>
       <c r="F44">
-        <v>2899.008</v>
+        <v>2968.032</v>
       </c>
       <c r="G44">
         <v>731.5</v>
@@ -4895,28 +4895,28 @@
         <v>488</v>
       </c>
       <c r="M44">
-        <v>219.7448064</v>
+        <v>224.9768256</v>
       </c>
       <c r="N44">
-        <v>268.2551936</v>
+        <v>263.0231744</v>
       </c>
       <c r="O44">
-        <v>40.23827903999999</v>
+        <v>39.45347615999999</v>
       </c>
       <c r="P44">
-        <v>228.01691456</v>
+        <v>223.56969824</v>
       </c>
       <c r="Q44">
-        <v>544.01691456</v>
+        <v>539.56969824</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1156211674280537</v>
+        <v>0.1167323657712888</v>
       </c>
       <c r="T44">
-        <v>1.324481745592612</v>
+        <v>1.345560767550592</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.220757832663844</v>
+        <v>2.169112301671661</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09424234848963461</v>
+        <v>0.09436381987099812</v>
       </c>
       <c r="C45">
-        <v>3453.530806230257</v>
+        <v>3373.214130526797</v>
       </c>
       <c r="D45">
-        <v>5690.062806230258</v>
+        <v>5678.770130526797</v>
       </c>
       <c r="E45">
-        <v>-1889.068</v>
+        <v>-1820.044</v>
       </c>
       <c r="F45">
-        <v>2968.032</v>
+        <v>3037.056</v>
       </c>
       <c r="G45">
         <v>731.5</v>
@@ -4977,28 +4977,28 @@
         <v>488</v>
       </c>
       <c r="M45">
-        <v>224.9768256</v>
+        <v>230.2088448</v>
       </c>
       <c r="N45">
-        <v>263.0231744</v>
+        <v>257.7911552</v>
       </c>
       <c r="O45">
-        <v>39.45347615999999</v>
+        <v>38.66867328</v>
       </c>
       <c r="P45">
-        <v>223.56969824</v>
+        <v>219.12248192</v>
       </c>
       <c r="Q45">
-        <v>539.56969824</v>
+        <v>535.1224819199999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1167323657712888</v>
+        <v>0.1178832497696395</v>
       </c>
       <c r="T45">
-        <v>1.345560767550592</v>
+        <v>1.367392611721356</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.169112301671661</v>
+        <v>2.119814294815487</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09436381987099812</v>
+        <v>0.0944852912523616</v>
       </c>
       <c r="C46">
-        <v>3373.214130526797</v>
+        <v>3292.942189632438</v>
       </c>
       <c r="D46">
-        <v>5678.770130526797</v>
+        <v>5667.522189632438</v>
       </c>
       <c r="E46">
-        <v>-1820.044</v>
+        <v>-1751.02</v>
       </c>
       <c r="F46">
-        <v>3037.056</v>
+        <v>3106.08</v>
       </c>
       <c r="G46">
         <v>731.5</v>
@@ -5059,28 +5059,28 @@
         <v>488</v>
       </c>
       <c r="M46">
-        <v>230.2088448</v>
+        <v>235.4408640000001</v>
       </c>
       <c r="N46">
-        <v>257.7911552</v>
+        <v>252.5591359999999</v>
       </c>
       <c r="O46">
-        <v>38.66867328</v>
+        <v>37.88387039999999</v>
       </c>
       <c r="P46">
-        <v>219.12248192</v>
+        <v>214.6752655999999</v>
       </c>
       <c r="Q46">
-        <v>535.1224819199999</v>
+        <v>530.6752655999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1178832497696395</v>
+        <v>0.1190759840952029</v>
       </c>
       <c r="T46">
-        <v>1.367392611721356</v>
+        <v>1.390018341134694</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.119814294815487</v>
+        <v>2.072707310486254</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0944852912523616</v>
+        <v>0.09460676263372511</v>
       </c>
       <c r="C47">
-        <v>3292.942189632438</v>
+        <v>3212.71471825391</v>
       </c>
       <c r="D47">
-        <v>5667.522189632438</v>
+        <v>5656.31871825391</v>
       </c>
       <c r="E47">
-        <v>-1751.02</v>
+        <v>-1681.996</v>
       </c>
       <c r="F47">
-        <v>3106.08</v>
+        <v>3175.104</v>
       </c>
       <c r="G47">
         <v>731.5</v>
@@ -5141,28 +5141,28 @@
         <v>488</v>
       </c>
       <c r="M47">
-        <v>235.4408640000001</v>
+        <v>240.6728832</v>
       </c>
       <c r="N47">
-        <v>252.5591359999999</v>
+        <v>247.3271168</v>
       </c>
       <c r="O47">
-        <v>37.88387039999999</v>
+        <v>37.09906751999999</v>
       </c>
       <c r="P47">
-        <v>214.6752655999999</v>
+        <v>210.22804928</v>
       </c>
       <c r="Q47">
-        <v>530.6752655999999</v>
+        <v>526.2280492800001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1190759840952029</v>
+        <v>0.1203128937661576</v>
       </c>
       <c r="T47">
-        <v>1.390018341134694</v>
+        <v>1.413482060526303</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.072707310486254</v>
+        <v>2.027648455910466</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09460676263372511</v>
+        <v>0.1004011340150886</v>
       </c>
       <c r="C48">
-        <v>3212.71471825391</v>
+        <v>2656.284652142645</v>
       </c>
       <c r="D48">
-        <v>5656.31871825391</v>
+        <v>5168.912652142646</v>
       </c>
       <c r="E48">
-        <v>-1681.996</v>
+        <v>-1612.972</v>
       </c>
       <c r="F48">
-        <v>3175.104</v>
+        <v>3244.128000000001</v>
       </c>
       <c r="G48">
         <v>731.5</v>
@@ -5223,45 +5223,45 @@
         <v>488</v>
       </c>
       <c r="M48">
-        <v>240.6728832</v>
+        <v>291.9715200000001</v>
       </c>
       <c r="N48">
-        <v>247.3271168</v>
+        <v>196.0284799999999</v>
       </c>
       <c r="O48">
-        <v>37.09906751999999</v>
+        <v>29.40427199999999</v>
       </c>
       <c r="P48">
-        <v>210.22804928</v>
+        <v>166.624208</v>
       </c>
       <c r="Q48">
-        <v>526.2280492800001</v>
+        <v>482.624208</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1203128937661576</v>
+        <v>0.1215964792737521</v>
       </c>
       <c r="T48">
-        <v>1.413482060526303</v>
+        <v>1.437831203291181</v>
       </c>
       <c r="U48">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V48">
         <v>0.15</v>
       </c>
       <c r="W48">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.027648455910466</v>
+        <v>1.671395895051681</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1004011340150886</v>
+        <v>0.1006433053964521</v>
       </c>
       <c r="C49">
-        <v>2656.284652142645</v>
+        <v>2568.712037615525</v>
       </c>
       <c r="D49">
-        <v>5168.912652142646</v>
+        <v>5150.364037615525</v>
       </c>
       <c r="E49">
-        <v>-1612.972</v>
+        <v>-1543.948</v>
       </c>
       <c r="F49">
-        <v>3244.128000000001</v>
+        <v>3313.152</v>
       </c>
       <c r="G49">
         <v>731.5</v>
@@ -5305,28 +5305,28 @@
         <v>488</v>
       </c>
       <c r="M49">
-        <v>291.9715200000001</v>
+        <v>298.18368</v>
       </c>
       <c r="N49">
-        <v>196.0284799999999</v>
+        <v>189.81632</v>
       </c>
       <c r="O49">
-        <v>29.40427199999999</v>
+        <v>28.47244799999999</v>
       </c>
       <c r="P49">
-        <v>166.624208</v>
+        <v>161.343872</v>
       </c>
       <c r="Q49">
-        <v>482.624208</v>
+        <v>477.343872</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1215964792737521</v>
+        <v>0.1229294334547155</v>
       </c>
       <c r="T49">
-        <v>1.437831203291181</v>
+        <v>1.463116851547015</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.671395895051681</v>
+        <v>1.636575147238105</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1006433053964521</v>
+        <v>0.1008854767778156</v>
       </c>
       <c r="C50">
-        <v>2568.712037615526</v>
+        <v>2481.272070286404</v>
       </c>
       <c r="D50">
-        <v>5150.364037615526</v>
+        <v>5131.948070286405</v>
       </c>
       <c r="E50">
-        <v>-1543.948</v>
+        <v>-1474.924</v>
       </c>
       <c r="F50">
-        <v>3313.152</v>
+        <v>3382.176</v>
       </c>
       <c r="G50">
         <v>731.5</v>
@@ -5387,28 +5387,28 @@
         <v>488</v>
       </c>
       <c r="M50">
-        <v>298.18368</v>
+        <v>304.39584</v>
       </c>
       <c r="N50">
-        <v>189.81632</v>
+        <v>183.60416</v>
       </c>
       <c r="O50">
-        <v>28.472448</v>
+        <v>27.540624</v>
       </c>
       <c r="P50">
-        <v>161.343872</v>
+        <v>156.063536</v>
       </c>
       <c r="Q50">
-        <v>477.343872</v>
+        <v>472.063536</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1229294334547155</v>
+        <v>0.124314660348658</v>
       </c>
       <c r="T50">
-        <v>1.463116851547015</v>
+        <v>1.489394093852098</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.636575147238105</v>
+        <v>1.603175654437327</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1008854767778156</v>
+        <v>0.1011276481591791</v>
       </c>
       <c r="C51">
-        <v>2481.272070286404</v>
+        <v>2393.963332319855</v>
       </c>
       <c r="D51">
-        <v>5131.948070286405</v>
+        <v>5113.663332319855</v>
       </c>
       <c r="E51">
-        <v>-1474.924</v>
+        <v>-1405.9</v>
       </c>
       <c r="F51">
-        <v>3382.176</v>
+        <v>3451.2</v>
       </c>
       <c r="G51">
         <v>731.5</v>
@@ -5469,28 +5469,28 @@
         <v>488</v>
       </c>
       <c r="M51">
-        <v>304.39584</v>
+        <v>310.608</v>
       </c>
       <c r="N51">
-        <v>183.60416</v>
+        <v>177.392</v>
       </c>
       <c r="O51">
-        <v>27.540624</v>
+        <v>26.6088</v>
       </c>
       <c r="P51">
-        <v>156.063536</v>
+        <v>150.7832</v>
       </c>
       <c r="Q51">
-        <v>472.063536</v>
+        <v>466.7832</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.124314660348658</v>
+        <v>0.1257552963183581</v>
       </c>
       <c r="T51">
-        <v>1.489394093852098</v>
+        <v>1.516722425849384</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.603175654437327</v>
+        <v>1.571112141348581</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1011276481591791</v>
+        <v>0.1013698195405426</v>
       </c>
       <c r="C52">
-        <v>2393.963332319855</v>
+        <v>2306.784426015273</v>
       </c>
       <c r="D52">
-        <v>5113.663332319855</v>
+        <v>5095.508426015273</v>
       </c>
       <c r="E52">
-        <v>-1405.9</v>
+        <v>-1336.876</v>
       </c>
       <c r="F52">
-        <v>3451.2</v>
+        <v>3520.224</v>
       </c>
       <c r="G52">
         <v>731.5</v>
@@ -5551,28 +5551,28 @@
         <v>488</v>
       </c>
       <c r="M52">
-        <v>310.608</v>
+        <v>316.82016</v>
       </c>
       <c r="N52">
-        <v>177.392</v>
+        <v>171.17984</v>
       </c>
       <c r="O52">
-        <v>26.6088</v>
+        <v>25.676976</v>
       </c>
       <c r="P52">
-        <v>150.7832</v>
+        <v>145.502864</v>
       </c>
       <c r="Q52">
-        <v>466.7832</v>
+        <v>461.502864</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1257552963183581</v>
+        <v>0.1272547337562093</v>
       </c>
       <c r="T52">
-        <v>1.516722425849384</v>
+        <v>1.545166199969009</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.571112141348581</v>
+        <v>1.540306020929981</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1013698195405426</v>
+        <v>0.1016119909219061</v>
       </c>
       <c r="C53">
-        <v>2306.784426015273</v>
+        <v>2219.733973450712</v>
       </c>
       <c r="D53">
-        <v>5095.508426015273</v>
+        <v>5077.481973450713</v>
       </c>
       <c r="E53">
-        <v>-1336.876</v>
+        <v>-1267.852</v>
       </c>
       <c r="F53">
-        <v>3520.224</v>
+        <v>3589.248000000001</v>
       </c>
       <c r="G53">
         <v>731.5</v>
@@ -5633,28 +5633,28 @@
         <v>488</v>
       </c>
       <c r="M53">
-        <v>316.82016</v>
+        <v>323.03232</v>
       </c>
       <c r="N53">
-        <v>171.17984</v>
+        <v>164.96768</v>
       </c>
       <c r="O53">
-        <v>25.676976</v>
+        <v>24.74515199999999</v>
       </c>
       <c r="P53">
-        <v>145.502864</v>
+        <v>140.222528</v>
       </c>
       <c r="Q53">
-        <v>461.502864</v>
+        <v>456.222528</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1272547337562093</v>
+        <v>0.1288166477539709</v>
       </c>
       <c r="T53">
-        <v>1.545166199969009</v>
+        <v>1.574795131343617</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.540306020929981</v>
+        <v>1.510684751296712</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1016119909219061</v>
+        <v>0.1288218743554981</v>
       </c>
       <c r="C54">
-        <v>2219.733973450712</v>
+        <v>706.5138480813971</v>
       </c>
       <c r="D54">
-        <v>5077.481973450713</v>
+        <v>3633.285848081397</v>
       </c>
       <c r="E54">
-        <v>-1267.852</v>
+        <v>-1198.828</v>
       </c>
       <c r="F54">
-        <v>3589.248000000001</v>
+        <v>3658.272</v>
       </c>
       <c r="G54">
         <v>731.5</v>
@@ -5715,45 +5715,45 @@
         <v>488</v>
       </c>
       <c r="M54">
-        <v>323.03232</v>
+        <v>537.0343296000001</v>
       </c>
       <c r="N54">
-        <v>164.96768</v>
+        <v>-49.03432960000009</v>
       </c>
       <c r="O54">
-        <v>24.74515199999999</v>
+        <v>-7.355149440000013</v>
       </c>
       <c r="P54">
-        <v>140.222528</v>
+        <v>-41.67918016000008</v>
       </c>
       <c r="Q54">
-        <v>456.222528</v>
+        <v>274.3208198399999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1288166477539709</v>
+        <v>0.1311125134246829</v>
       </c>
       <c r="T54">
-        <v>1.574795131343617</v>
+        <v>1.618346854742171</v>
       </c>
       <c r="U54">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.15</v>
+        <v>0.1363041354442306</v>
       </c>
       <c r="W54">
-        <v>0.0765</v>
+        <v>0.126790552916787</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y54">
-        <v>1.510684751296712</v>
+        <v>0.9086942362948708</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1288218743554981</v>
+        <v>0.129831874355498</v>
       </c>
       <c r="C55">
-        <v>706.5138480813971</v>
+        <v>599.5311860090228</v>
       </c>
       <c r="D55">
-        <v>3633.285848081397</v>
+        <v>3595.327186009024</v>
       </c>
       <c r="E55">
-        <v>-1198.828</v>
+        <v>-1129.804</v>
       </c>
       <c r="F55">
-        <v>3658.272</v>
+        <v>3727.296000000001</v>
       </c>
       <c r="G55">
         <v>731.5</v>
@@ -5797,37 +5797,37 @@
         <v>488</v>
       </c>
       <c r="M55">
-        <v>537.0343296000001</v>
+        <v>547.1670528000002</v>
       </c>
       <c r="N55">
-        <v>-49.03432960000009</v>
+        <v>-59.16705280000019</v>
       </c>
       <c r="O55">
-        <v>-7.355149440000013</v>
+        <v>-8.875057920000028</v>
       </c>
       <c r="P55">
-        <v>-41.67918016000008</v>
+        <v>-50.29199488000016</v>
       </c>
       <c r="Q55">
-        <v>274.3208198399999</v>
+        <v>265.7080051199998</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1311125134246829</v>
+        <v>0.1329671332817412</v>
       </c>
       <c r="T55">
-        <v>1.618346854742171</v>
+        <v>1.653528308106131</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.1363041354442306</v>
+        <v>0.1337799847878559</v>
       </c>
       <c r="W55">
-        <v>0.126790552916787</v>
+        <v>0.1271610982331428</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.9086942362948708</v>
+        <v>0.891866565252373</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.129831874355498</v>
+        <v>0.130841874355498</v>
       </c>
       <c r="C56">
-        <v>599.5311860090228</v>
+        <v>493.3334675830538</v>
       </c>
       <c r="D56">
-        <v>3595.327186009024</v>
+        <v>3558.153467583054</v>
       </c>
       <c r="E56">
-        <v>-1129.804</v>
+        <v>-1060.78</v>
       </c>
       <c r="F56">
-        <v>3727.296000000001</v>
+        <v>3796.320000000001</v>
       </c>
       <c r="G56">
         <v>731.5</v>
@@ -5879,37 +5879,37 @@
         <v>488</v>
       </c>
       <c r="M56">
-        <v>547.1670528000002</v>
+        <v>557.2997760000002</v>
       </c>
       <c r="N56">
-        <v>-59.16705280000019</v>
+        <v>-69.29977600000018</v>
       </c>
       <c r="O56">
-        <v>-8.875057920000028</v>
+        <v>-10.39496640000003</v>
       </c>
       <c r="P56">
-        <v>-50.29199488000016</v>
+        <v>-58.90480960000015</v>
       </c>
       <c r="Q56">
-        <v>265.7080051199998</v>
+        <v>257.0951903999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1329671332817412</v>
+        <v>0.1349041806880021</v>
       </c>
       <c r="T56">
-        <v>1.653528308106131</v>
+        <v>1.690273381619601</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.1337799847878559</v>
+        <v>0.1313476214280767</v>
       </c>
       <c r="W56">
-        <v>0.1271610982331428</v>
+        <v>0.1275181691743583</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.891866565252373</v>
+        <v>0.8756508095205117</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.130841874355498</v>
+        <v>0.1318518743554981</v>
       </c>
       <c r="C57">
-        <v>493.3334675830538</v>
+        <v>387.8965943037042</v>
       </c>
       <c r="D57">
-        <v>3558.153467583054</v>
+        <v>3521.740594303704</v>
       </c>
       <c r="E57">
-        <v>-1060.78</v>
+        <v>-991.7559999999999</v>
       </c>
       <c r="F57">
-        <v>3796.320000000001</v>
+        <v>3865.344000000001</v>
       </c>
       <c r="G57">
         <v>731.5</v>
@@ -5961,37 +5961,37 @@
         <v>488</v>
       </c>
       <c r="M57">
-        <v>557.2997760000002</v>
+        <v>567.4324992000002</v>
       </c>
       <c r="N57">
-        <v>-69.29977600000018</v>
+        <v>-79.43249920000017</v>
       </c>
       <c r="O57">
-        <v>-10.39496640000003</v>
+        <v>-11.91487488000002</v>
       </c>
       <c r="P57">
-        <v>-58.90480960000015</v>
+        <v>-67.51762432000014</v>
       </c>
       <c r="Q57">
-        <v>257.0951903999999</v>
+        <v>248.4823756799998</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1349041806880021</v>
+        <v>0.1369292757036385</v>
       </c>
       <c r="T57">
-        <v>1.690273381619601</v>
+        <v>1.728688685747319</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.1313476214280767</v>
+        <v>0.1290021281882897</v>
       </c>
       <c r="W57">
-        <v>0.1275181691743583</v>
+        <v>0.1278624875819591</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8756508095205117</v>
+        <v>0.8600141879219312</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1318518743554981</v>
+        <v>0.132861874355498</v>
       </c>
       <c r="C58">
-        <v>387.8965943037042</v>
+        <v>283.1974441401494</v>
       </c>
       <c r="D58">
-        <v>3521.740594303704</v>
+        <v>3486.06544414015</v>
       </c>
       <c r="E58">
-        <v>-991.7559999999999</v>
+        <v>-922.7319999999995</v>
       </c>
       <c r="F58">
-        <v>3865.344000000001</v>
+        <v>3934.368000000001</v>
       </c>
       <c r="G58">
         <v>731.5</v>
@@ -6043,37 +6043,37 @@
         <v>488</v>
       </c>
       <c r="M58">
-        <v>567.4324992000002</v>
+        <v>577.5652224000002</v>
       </c>
       <c r="N58">
-        <v>-79.43249920000017</v>
+        <v>-89.56522240000015</v>
       </c>
       <c r="O58">
-        <v>-11.91487488000002</v>
+        <v>-13.43478336000002</v>
       </c>
       <c r="P58">
-        <v>-67.51762432000014</v>
+        <v>-76.13043904000013</v>
       </c>
       <c r="Q58">
-        <v>248.4823756799998</v>
+        <v>239.8695609599999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1369292757036385</v>
+        <v>0.1390485611851185</v>
       </c>
       <c r="T58">
-        <v>1.728688685747319</v>
+        <v>1.768890748206559</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.1290021281882897</v>
+        <v>0.1267389329569162</v>
       </c>
       <c r="W58">
-        <v>0.1278624875819591</v>
+        <v>0.1281947246419247</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8600141879219312</v>
+        <v>0.8449262197127745</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.132861874355498</v>
+        <v>0.133871874355498</v>
       </c>
       <c r="C59">
-        <v>283.1974441401494</v>
+        <v>179.2138225684785</v>
       </c>
       <c r="D59">
-        <v>3486.06544414015</v>
+        <v>3451.10582256848</v>
       </c>
       <c r="E59">
-        <v>-922.7319999999995</v>
+        <v>-853.7079999999996</v>
       </c>
       <c r="F59">
-        <v>3934.368000000001</v>
+        <v>4003.392000000001</v>
       </c>
       <c r="G59">
         <v>731.5</v>
@@ -6125,37 +6125,37 @@
         <v>488</v>
       </c>
       <c r="M59">
-        <v>577.5652224000002</v>
+        <v>587.6979456000001</v>
       </c>
       <c r="N59">
-        <v>-89.56522240000015</v>
+        <v>-99.69794560000014</v>
       </c>
       <c r="O59">
-        <v>-13.43478336000002</v>
+        <v>-14.95469184000002</v>
       </c>
       <c r="P59">
-        <v>-76.13043904000013</v>
+        <v>-84.74325376000012</v>
       </c>
       <c r="Q59">
-        <v>239.8695609599999</v>
+        <v>231.2567462399999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1390485611851185</v>
+        <v>0.1412687650228595</v>
       </c>
       <c r="T59">
-        <v>1.768890748206559</v>
+        <v>1.81100719459243</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.1267389329569162</v>
+        <v>0.1245537789404176</v>
       </c>
       <c r="W59">
-        <v>0.1281947246419247</v>
+        <v>0.1285155052515467</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8449262197127745</v>
+        <v>0.8303585262694508</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.133871874355498</v>
+        <v>0.134881874355498</v>
       </c>
       <c r="C60">
-        <v>179.2138225684794</v>
+        <v>75.92441652645084</v>
       </c>
       <c r="D60">
-        <v>3451.10582256848</v>
+        <v>3416.840416526451</v>
       </c>
       <c r="E60">
-        <v>-853.7080000000005</v>
+        <v>-784.6840000000002</v>
       </c>
       <c r="F60">
-        <v>4003.392</v>
+        <v>4072.416</v>
       </c>
       <c r="G60">
         <v>731.5</v>
@@ -6207,37 +6207,37 @@
         <v>488</v>
       </c>
       <c r="M60">
-        <v>587.6979456</v>
+        <v>597.8306688000001</v>
       </c>
       <c r="N60">
-        <v>-99.69794560000003</v>
+        <v>-109.8306688000001</v>
       </c>
       <c r="O60">
-        <v>-14.95469184</v>
+        <v>-16.47460032000002</v>
       </c>
       <c r="P60">
-        <v>-84.74325376000002</v>
+        <v>-93.3560684800001</v>
       </c>
       <c r="Q60">
-        <v>231.25674624</v>
+        <v>222.6439315199999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1412687650228594</v>
+        <v>0.1435972714868316</v>
       </c>
       <c r="T60">
-        <v>1.81100719459243</v>
+        <v>1.855178101777611</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.1245537789404176</v>
+        <v>0.1224426979414275</v>
       </c>
       <c r="W60">
-        <v>0.1285155052515467</v>
+        <v>0.1288254119421985</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8303585262694511</v>
+        <v>0.81628465294285</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.134881874355498</v>
+        <v>0.135891874355498</v>
       </c>
       <c r="C61">
-        <v>75.92441652645084</v>
+        <v>-26.69124891567662</v>
       </c>
       <c r="D61">
-        <v>3416.840416526451</v>
+        <v>3383.248751084323</v>
       </c>
       <c r="E61">
-        <v>-784.6840000000002</v>
+        <v>-715.6599999999999</v>
       </c>
       <c r="F61">
-        <v>4072.416</v>
+        <v>4141.440000000001</v>
       </c>
       <c r="G61">
         <v>731.5</v>
@@ -6289,37 +6289,37 @@
         <v>488</v>
       </c>
       <c r="M61">
-        <v>597.8306688000001</v>
+        <v>607.9633920000001</v>
       </c>
       <c r="N61">
-        <v>-109.8306688000001</v>
+        <v>-119.9633920000001</v>
       </c>
       <c r="O61">
-        <v>-16.47460032000002</v>
+        <v>-17.99450880000002</v>
       </c>
       <c r="P61">
-        <v>-93.3560684800001</v>
+        <v>-101.9688832000001</v>
       </c>
       <c r="Q61">
-        <v>222.6439315199999</v>
+        <v>214.0311167999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1435972714868316</v>
+        <v>0.1460422032740024</v>
       </c>
       <c r="T61">
-        <v>1.855178101777611</v>
+        <v>1.901557554322051</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.1224426979414275</v>
+        <v>0.1204019863090704</v>
       </c>
       <c r="W61">
-        <v>0.1288254119421985</v>
+        <v>0.1291249884098285</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.81628465294285</v>
+        <v>0.8026799087271359</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.135891874355498</v>
+        <v>0.1706815092170308</v>
       </c>
       <c r="C62">
-        <v>-26.69124891567662</v>
+        <v>-951.582103809485</v>
       </c>
       <c r="D62">
-        <v>3383.248751084323</v>
+        <v>2527.381896190515</v>
       </c>
       <c r="E62">
-        <v>-715.6599999999999</v>
+        <v>-646.6360000000004</v>
       </c>
       <c r="F62">
-        <v>4141.440000000001</v>
+        <v>4210.464</v>
       </c>
       <c r="G62">
         <v>731.5</v>
@@ -6371,45 +6371,45 @@
         <v>488</v>
       </c>
       <c r="M62">
-        <v>607.9633920000001</v>
+        <v>845.4611712</v>
       </c>
       <c r="N62">
-        <v>-119.9633920000001</v>
+        <v>-357.4611712</v>
       </c>
       <c r="O62">
-        <v>-17.99450880000002</v>
+        <v>-53.61917567999999</v>
       </c>
       <c r="P62">
-        <v>-101.9688832000001</v>
+        <v>-303.84199552</v>
       </c>
       <c r="Q62">
-        <v>214.0311167999999</v>
+        <v>12.15800448000005</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1460422032740024</v>
+        <v>0.1507654260798301</v>
       </c>
       <c r="T62">
-        <v>1.901557554322051</v>
+        <v>1.991155345609798</v>
       </c>
       <c r="U62">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1204019863090704</v>
+        <v>0.08657996664247045</v>
       </c>
       <c r="W62">
-        <v>0.1291249884098285</v>
+        <v>0.1834147426981919</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.8026799087271359</v>
+        <v>0.5771997776164697</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1706815092170308</v>
+        <v>0.1722315092170308</v>
       </c>
       <c r="C63">
-        <v>-951.582103809485</v>
+        <v>-1048.774201305593</v>
       </c>
       <c r="D63">
-        <v>2527.381896190515</v>
+        <v>2499.213798694408</v>
       </c>
       <c r="E63">
-        <v>-646.6360000000004</v>
+        <v>-577.6120000000001</v>
       </c>
       <c r="F63">
-        <v>4210.464</v>
+        <v>4279.488</v>
       </c>
       <c r="G63">
         <v>731.5</v>
@@ -6453,37 +6453,37 @@
         <v>488</v>
       </c>
       <c r="M63">
-        <v>845.4611712</v>
+        <v>859.3211904000001</v>
       </c>
       <c r="N63">
-        <v>-357.4611712</v>
+        <v>-371.3211904000001</v>
       </c>
       <c r="O63">
-        <v>-53.61917567999999</v>
+        <v>-55.69817856000001</v>
       </c>
       <c r="P63">
-        <v>-303.84199552</v>
+        <v>-315.6230118400001</v>
       </c>
       <c r="Q63">
-        <v>12.15800448000005</v>
+        <v>0.3769881599999394</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1507654260798301</v>
+        <v>0.1535276741345625</v>
       </c>
       <c r="T63">
-        <v>1.991155345609798</v>
+        <v>2.043554170494266</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.08657996664247045</v>
+        <v>0.08518351556759188</v>
       </c>
       <c r="W63">
-        <v>0.1834147426981919</v>
+        <v>0.1836951500740276</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5771997776164697</v>
+        <v>0.5678901037839459</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1722315092170308</v>
+        <v>0.1737815092170308</v>
       </c>
       <c r="C64">
-        <v>-1048.774201305593</v>
+        <v>-1145.345343063397</v>
       </c>
       <c r="D64">
-        <v>2499.213798694408</v>
+        <v>2471.666656936604</v>
       </c>
       <c r="E64">
-        <v>-577.6120000000001</v>
+        <v>-508.5879999999997</v>
       </c>
       <c r="F64">
-        <v>4279.488</v>
+        <v>4348.512000000001</v>
       </c>
       <c r="G64">
         <v>731.5</v>
@@ -6535,37 +6535,37 @@
         <v>488</v>
       </c>
       <c r="M64">
-        <v>859.3211904000001</v>
+        <v>873.1812096000001</v>
       </c>
       <c r="N64">
-        <v>-371.3211904000001</v>
+        <v>-385.1812096000001</v>
       </c>
       <c r="O64">
-        <v>-55.69817856000001</v>
+        <v>-57.77718144000001</v>
       </c>
       <c r="P64">
-        <v>-315.6230118400001</v>
+        <v>-327.4040281600001</v>
       </c>
       <c r="Q64">
-        <v>0.3769881599999394</v>
+        <v>-11.40402816000011</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1535276741345625</v>
+        <v>0.1564392328949561</v>
       </c>
       <c r="T64">
-        <v>2.043554170494266</v>
+        <v>2.098785364291408</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.08518351556759188</v>
+        <v>0.0838313962728682</v>
       </c>
       <c r="W64">
-        <v>0.1836951500740276</v>
+        <v>0.1839666556284081</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5678901037839459</v>
+        <v>0.5588759751524547</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1737815092170308</v>
+        <v>0.1753315092170308</v>
       </c>
       <c r="C65">
-        <v>-1145.345343063397</v>
+        <v>-1241.315838351741</v>
       </c>
       <c r="D65">
-        <v>2471.666656936604</v>
+        <v>2444.720161648259</v>
       </c>
       <c r="E65">
-        <v>-508.5879999999997</v>
+        <v>-439.5640000000003</v>
       </c>
       <c r="F65">
-        <v>4348.512000000001</v>
+        <v>4417.536</v>
       </c>
       <c r="G65">
         <v>731.5</v>
@@ -6617,37 +6617,37 @@
         <v>488</v>
       </c>
       <c r="M65">
-        <v>873.1812096000001</v>
+        <v>887.0412288</v>
       </c>
       <c r="N65">
-        <v>-385.1812096000001</v>
+        <v>-399.0412288</v>
       </c>
       <c r="O65">
-        <v>-57.77718144000001</v>
+        <v>-59.85618432</v>
       </c>
       <c r="P65">
-        <v>-327.4040281600001</v>
+        <v>-339.18504448</v>
       </c>
       <c r="Q65">
-        <v>-11.40402816000011</v>
+        <v>-23.18504447999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1564392328949561</v>
+        <v>0.159512544919816</v>
       </c>
       <c r="T65">
-        <v>2.098785364291408</v>
+        <v>2.157084957743948</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.0838313962728682</v>
+        <v>0.08252153070610466</v>
       </c>
       <c r="W65">
-        <v>0.1839666556284081</v>
+        <v>0.1842296766342142</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5588759751524547</v>
+        <v>0.5501435380406976</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1753315092170308</v>
+        <v>0.1768815092170308</v>
       </c>
       <c r="C66">
-        <v>-1241.315838351741</v>
+        <v>-1336.705120331672</v>
       </c>
       <c r="D66">
-        <v>2444.720161648259</v>
+        <v>2418.354879668328</v>
       </c>
       <c r="E66">
-        <v>-439.5640000000003</v>
+        <v>-370.54</v>
       </c>
       <c r="F66">
-        <v>4417.536</v>
+        <v>4486.56</v>
       </c>
       <c r="G66">
         <v>731.5</v>
@@ -6699,37 +6699,37 @@
         <v>488</v>
       </c>
       <c r="M66">
-        <v>887.0412288</v>
+        <v>900.9012480000001</v>
       </c>
       <c r="N66">
-        <v>-399.0412288</v>
+        <v>-412.9012480000001</v>
       </c>
       <c r="O66">
-        <v>-59.85618432</v>
+        <v>-61.93518720000002</v>
       </c>
       <c r="P66">
-        <v>-339.18504448</v>
+        <v>-350.9660608000001</v>
       </c>
       <c r="Q66">
-        <v>-23.18504447999999</v>
+        <v>-34.96606080000009</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.159512544919816</v>
+        <v>0.1627614747746679</v>
       </c>
       <c r="T66">
-        <v>2.157084957743948</v>
+        <v>2.218715956536632</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.08252153070610466</v>
+        <v>0.08125196869524148</v>
       </c>
       <c r="W66">
-        <v>0.1842296766342142</v>
+        <v>0.1844846046859955</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5501435380406976</v>
+        <v>0.5416797913016099</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1768815092170308</v>
+        <v>0.1784315092170309</v>
       </c>
       <c r="C67">
-        <v>-1336.705120331672</v>
+        <v>-1431.531792794663</v>
       </c>
       <c r="D67">
-        <v>2418.354879668328</v>
+        <v>2392.552207205338</v>
       </c>
       <c r="E67">
-        <v>-370.54</v>
+        <v>-301.5159999999996</v>
       </c>
       <c r="F67">
-        <v>4486.56</v>
+        <v>4555.584000000001</v>
       </c>
       <c r="G67">
         <v>731.5</v>
@@ -6781,37 +6781,37 @@
         <v>488</v>
       </c>
       <c r="M67">
-        <v>900.9012480000001</v>
+        <v>914.7612672000001</v>
       </c>
       <c r="N67">
-        <v>-412.9012480000001</v>
+        <v>-426.7612672000001</v>
       </c>
       <c r="O67">
-        <v>-61.93518720000002</v>
+        <v>-64.01419008000002</v>
       </c>
       <c r="P67">
-        <v>-350.9660608000001</v>
+        <v>-362.7470771200001</v>
       </c>
       <c r="Q67">
-        <v>-34.96606080000009</v>
+        <v>-46.74707712000009</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1627614747746679</v>
+        <v>0.1662015181503934</v>
       </c>
       <c r="T67">
-        <v>2.218715956536632</v>
+        <v>2.283972308199474</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.08125196869524148</v>
+        <v>0.0800208782604651</v>
       </c>
       <c r="W67">
-        <v>0.1844846046859955</v>
+        <v>0.1847318076452986</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5416797913016099</v>
+        <v>0.533472521736434</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1784315092170309</v>
+        <v>0.1799815092170309</v>
       </c>
       <c r="C68">
-        <v>-1431.531792794663</v>
+        <v>-1525.813673940373</v>
       </c>
       <c r="D68">
-        <v>2392.552207205338</v>
+        <v>2367.294326059628</v>
       </c>
       <c r="E68">
-        <v>-301.5159999999996</v>
+        <v>-232.4919999999993</v>
       </c>
       <c r="F68">
-        <v>4555.584000000001</v>
+        <v>4624.608000000001</v>
       </c>
       <c r="G68">
         <v>731.5</v>
@@ -6863,37 +6863,37 @@
         <v>488</v>
       </c>
       <c r="M68">
-        <v>914.7612672000001</v>
+        <v>928.6212864000003</v>
       </c>
       <c r="N68">
-        <v>-426.7612672000001</v>
+        <v>-440.6212864000003</v>
       </c>
       <c r="O68">
-        <v>-64.01419008000002</v>
+        <v>-66.09319296000004</v>
       </c>
       <c r="P68">
-        <v>-362.7470771200001</v>
+        <v>-374.5280934400002</v>
       </c>
       <c r="Q68">
-        <v>-46.74707712000009</v>
+        <v>-58.52809344000025</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1662015181503934</v>
+        <v>0.1698500490034356</v>
       </c>
       <c r="T68">
-        <v>2.283972308199474</v>
+        <v>2.353183590266125</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.0800208782604651</v>
+        <v>0.07882653679389098</v>
       </c>
       <c r="W68">
-        <v>0.1847318076452986</v>
+        <v>0.1849716314117867</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.533472521736434</v>
+        <v>0.5255102452926066</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1799815092170309</v>
+        <v>0.1815315092170308</v>
       </c>
       <c r="C69">
-        <v>-1525.813673940373</v>
+        <v>-1619.567837410451</v>
       </c>
       <c r="D69">
-        <v>2367.294326059628</v>
+        <v>2342.56416258955</v>
       </c>
       <c r="E69">
-        <v>-232.4919999999993</v>
+        <v>-163.4679999999998</v>
       </c>
       <c r="F69">
-        <v>4624.608000000001</v>
+        <v>4693.632000000001</v>
       </c>
       <c r="G69">
         <v>731.5</v>
@@ -6945,37 +6945,37 @@
         <v>488</v>
       </c>
       <c r="M69">
-        <v>928.6212864000003</v>
+        <v>942.4813056000002</v>
       </c>
       <c r="N69">
-        <v>-440.6212864000003</v>
+        <v>-454.4813056000002</v>
       </c>
       <c r="O69">
-        <v>-66.09319296000004</v>
+        <v>-68.17219584000001</v>
       </c>
       <c r="P69">
-        <v>-374.5280934400002</v>
+        <v>-386.3091097600001</v>
       </c>
       <c r="Q69">
-        <v>-58.52809344000025</v>
+        <v>-70.30910976000013</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1698500490034356</v>
+        <v>0.173726613034793</v>
       </c>
       <c r="T69">
-        <v>2.353183590266125</v>
+        <v>2.426720577461941</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.07882653679389098</v>
+        <v>0.07766732301751024</v>
       </c>
       <c r="W69">
-        <v>0.1849716314117867</v>
+        <v>0.185204401538084</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5255102452926066</v>
+        <v>0.5177821534500683</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1815315092170308</v>
+        <v>0.1830815092170309</v>
       </c>
       <c r="C70">
-        <v>-1619.567837410451</v>
+        <v>-1712.810650776939</v>
       </c>
       <c r="D70">
-        <v>2342.56416258955</v>
+        <v>2318.345349223061</v>
       </c>
       <c r="E70">
-        <v>-163.4679999999998</v>
+        <v>-94.44399999999951</v>
       </c>
       <c r="F70">
-        <v>4693.632000000001</v>
+        <v>4762.656000000001</v>
       </c>
       <c r="G70">
         <v>731.5</v>
@@ -7027,37 +7027,37 @@
         <v>488</v>
       </c>
       <c r="M70">
-        <v>942.4813056000002</v>
+        <v>956.3413248000002</v>
       </c>
       <c r="N70">
-        <v>-454.4813056000002</v>
+        <v>-468.3413248000002</v>
       </c>
       <c r="O70">
-        <v>-68.17219584000001</v>
+        <v>-70.25119872000002</v>
       </c>
       <c r="P70">
-        <v>-386.3091097600001</v>
+        <v>-398.0901260800001</v>
       </c>
       <c r="Q70">
-        <v>-70.30910976000013</v>
+        <v>-82.09012608000012</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.173726613034793</v>
+        <v>0.1778532779713993</v>
       </c>
       <c r="T70">
-        <v>2.426720577461941</v>
+        <v>2.505001886412327</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.07766732301751024</v>
+        <v>0.07654170964044488</v>
       </c>
       <c r="W70">
-        <v>0.185204401538084</v>
+        <v>0.1854304247041987</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5177821534500683</v>
+        <v>0.5102780642696325</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1830815092170309</v>
+        <v>0.1846315092170308</v>
       </c>
       <c r="C71">
-        <v>-1712.810650776939</v>
+        <v>-1805.557811667606</v>
       </c>
       <c r="D71">
-        <v>2318.345349223061</v>
+        <v>2294.622188332395</v>
       </c>
       <c r="E71">
-        <v>-94.44399999999951</v>
+        <v>-25.41999999999916</v>
       </c>
       <c r="F71">
-        <v>4762.656000000001</v>
+        <v>4831.680000000001</v>
       </c>
       <c r="G71">
         <v>731.5</v>
@@ -7109,37 +7109,37 @@
         <v>488</v>
       </c>
       <c r="M71">
-        <v>956.3413248000002</v>
+        <v>970.2013440000003</v>
       </c>
       <c r="N71">
-        <v>-468.3413248000002</v>
+        <v>-482.2013440000003</v>
       </c>
       <c r="O71">
-        <v>-70.25119872000002</v>
+        <v>-72.33020160000004</v>
       </c>
       <c r="P71">
-        <v>-398.0901260800001</v>
+        <v>-409.8711424000003</v>
       </c>
       <c r="Q71">
-        <v>-82.09012608000012</v>
+        <v>-93.87114240000028</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1778532779713993</v>
+        <v>0.1822550539037792</v>
       </c>
       <c r="T71">
-        <v>2.505001886412327</v>
+        <v>2.588501949292737</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.07654170964044488</v>
+        <v>0.07544825664558137</v>
       </c>
       <c r="W71">
-        <v>0.1854304247041987</v>
+        <v>0.1856499900655673</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5102780642696325</v>
+        <v>0.5029883776372092</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1846315092170308</v>
+        <v>0.2113703120253238</v>
       </c>
       <c r="C72">
-        <v>-1805.557811667606</v>
+        <v>-2218.864308000309</v>
       </c>
       <c r="D72">
-        <v>2294.622188332395</v>
+        <v>1950.339691999691</v>
       </c>
       <c r="E72">
-        <v>-25.41999999999916</v>
+        <v>43.60400000000027</v>
       </c>
       <c r="F72">
-        <v>4831.680000000001</v>
+        <v>4900.704000000001</v>
       </c>
       <c r="G72">
         <v>731.5</v>
@@ -7191,45 +7191,45 @@
         <v>488</v>
       </c>
       <c r="M72">
-        <v>970.2013440000003</v>
+        <v>1155.5860032</v>
       </c>
       <c r="N72">
-        <v>-482.2013440000003</v>
+        <v>-667.5860032000003</v>
       </c>
       <c r="O72">
-        <v>-72.33020160000004</v>
+        <v>-100.13790048</v>
       </c>
       <c r="P72">
-        <v>-409.8711424000003</v>
+        <v>-567.4481027200002</v>
       </c>
       <c r="Q72">
-        <v>-93.87114240000028</v>
+        <v>-251.4481027200002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1822550539037792</v>
+        <v>0.1881286861359542</v>
       </c>
       <c r="T72">
-        <v>2.588501949292737</v>
+        <v>2.699922582295708</v>
       </c>
       <c r="U72">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.07544825664558137</v>
+        <v>0.06334448478719681</v>
       </c>
       <c r="W72">
-        <v>0.1856499900655673</v>
+        <v>0.220863370487179</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y72">
-        <v>0.5029883776372092</v>
+        <v>0.4222965652479789</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2113703120253237</v>
+        <v>0.2132703120253238</v>
       </c>
       <c r="C73">
-        <v>-2218.864308000307</v>
+        <v>-2308.462366247597</v>
       </c>
       <c r="D73">
-        <v>1950.339691999693</v>
+        <v>1929.765633752403</v>
       </c>
       <c r="E73">
-        <v>43.60399999999936</v>
+        <v>112.6279999999997</v>
       </c>
       <c r="F73">
-        <v>4900.704</v>
+        <v>4969.728</v>
       </c>
       <c r="G73">
         <v>731.5</v>
@@ -7273,37 +7273,37 @@
         <v>488</v>
       </c>
       <c r="M73">
-        <v>1155.5860032</v>
+        <v>1171.8618624</v>
       </c>
       <c r="N73">
-        <v>-667.5860032000001</v>
+        <v>-683.8618624000001</v>
       </c>
       <c r="O73">
-        <v>-100.13790048</v>
+        <v>-102.57927936</v>
       </c>
       <c r="P73">
-        <v>-567.4481027200001</v>
+        <v>-581.2825830400001</v>
       </c>
       <c r="Q73">
-        <v>-251.4481027200001</v>
+        <v>-265.2825830400001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.188128686135954</v>
+        <v>0.1932118534979525</v>
       </c>
       <c r="T73">
-        <v>2.699922582295706</v>
+        <v>2.796348388806268</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.06334448478719684</v>
+        <v>0.06246470027626355</v>
       </c>
       <c r="W73">
-        <v>0.220863370487179</v>
+        <v>0.2210708236748571</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4222965652479789</v>
+        <v>0.4164313351750903</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2132703120253238</v>
+        <v>0.2151703120253238</v>
       </c>
       <c r="C74">
-        <v>-2308.462366247597</v>
+        <v>-2397.630885787055</v>
       </c>
       <c r="D74">
-        <v>1929.765633752403</v>
+        <v>1909.621114212945</v>
       </c>
       <c r="E74">
-        <v>112.6279999999997</v>
+        <v>181.652</v>
       </c>
       <c r="F74">
-        <v>4969.728</v>
+        <v>5038.752</v>
       </c>
       <c r="G74">
         <v>731.5</v>
@@ -7355,37 +7355,37 @@
         <v>488</v>
       </c>
       <c r="M74">
-        <v>1171.8618624</v>
+        <v>1188.1377216</v>
       </c>
       <c r="N74">
-        <v>-683.8618624000001</v>
+        <v>-700.1377216000001</v>
       </c>
       <c r="O74">
-        <v>-102.57927936</v>
+        <v>-105.02065824</v>
       </c>
       <c r="P74">
-        <v>-581.2825830400001</v>
+        <v>-595.1170633600001</v>
       </c>
       <c r="Q74">
-        <v>-265.2825830400001</v>
+        <v>-279.1170633600001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1932118534979525</v>
+        <v>0.1986715517756544</v>
       </c>
       <c r="T74">
-        <v>2.796348388806268</v>
+        <v>2.899916847650944</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.06246470027626355</v>
+        <v>0.0616090194505613</v>
       </c>
       <c r="W74">
-        <v>0.2210708236748571</v>
+        <v>0.2212725932135577</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4164313351750903</v>
+        <v>0.4107267963370754</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2151703120253238</v>
+        <v>0.2170703120253238</v>
       </c>
       <c r="C75">
-        <v>-2397.630885787055</v>
+        <v>-2486.383179310365</v>
       </c>
       <c r="D75">
-        <v>1909.621114212945</v>
+        <v>1889.892820689635</v>
       </c>
       <c r="E75">
-        <v>181.652</v>
+        <v>250.6760000000004</v>
       </c>
       <c r="F75">
-        <v>5038.752</v>
+        <v>5107.776000000001</v>
       </c>
       <c r="G75">
         <v>731.5</v>
@@ -7437,37 +7437,37 @@
         <v>488</v>
       </c>
       <c r="M75">
-        <v>1188.1377216</v>
+        <v>1204.4135808</v>
       </c>
       <c r="N75">
-        <v>-700.1377216000001</v>
+        <v>-716.4135808000003</v>
       </c>
       <c r="O75">
-        <v>-105.02065824</v>
+        <v>-107.46203712</v>
       </c>
       <c r="P75">
-        <v>-595.1170633600001</v>
+        <v>-608.9515436800002</v>
       </c>
       <c r="Q75">
-        <v>-279.1170633600001</v>
+        <v>-292.9515436800002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1986715517756544</v>
+        <v>0.2045512268439487</v>
       </c>
       <c r="T75">
-        <v>2.899916847650944</v>
+        <v>3.011452111022134</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.0616090194505613</v>
+        <v>0.06077646513366182</v>
       </c>
       <c r="W75">
-        <v>0.2212725932135577</v>
+        <v>0.2214689095214825</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4107267963370754</v>
+        <v>0.4051764342244121</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2170703120253238</v>
+        <v>0.2189703120253238</v>
       </c>
       <c r="C76">
-        <v>-2486.383179310365</v>
+        <v>-2574.732015000915</v>
       </c>
       <c r="D76">
-        <v>1889.892820689635</v>
+        <v>1870.567984999085</v>
       </c>
       <c r="E76">
-        <v>250.6760000000004</v>
+        <v>319.6999999999998</v>
       </c>
       <c r="F76">
-        <v>5107.776000000001</v>
+        <v>5176.8</v>
       </c>
       <c r="G76">
         <v>731.5</v>
@@ -7519,37 +7519,37 @@
         <v>488</v>
       </c>
       <c r="M76">
-        <v>1204.4135808</v>
+        <v>1220.68944</v>
       </c>
       <c r="N76">
-        <v>-716.4135808000003</v>
+        <v>-732.6894400000001</v>
       </c>
       <c r="O76">
-        <v>-107.46203712</v>
+        <v>-109.903416</v>
       </c>
       <c r="P76">
-        <v>-608.9515436800002</v>
+        <v>-622.7860240000001</v>
       </c>
       <c r="Q76">
-        <v>-292.9515436800002</v>
+        <v>-306.7860240000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2045512268439487</v>
+        <v>0.2109012759177067</v>
       </c>
       <c r="T76">
-        <v>3.011452111022134</v>
+        <v>3.13191019546302</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.06077646513366182</v>
+        <v>0.05996611226521301</v>
       </c>
       <c r="W76">
-        <v>0.2214689095214825</v>
+        <v>0.2216599907278628</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4051764342244121</v>
+        <v>0.3997740817680867</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2189703120253238</v>
+        <v>0.2208703120253238</v>
       </c>
       <c r="C77">
-        <v>-2574.732015000915</v>
+        <v>-2662.689644090982</v>
       </c>
       <c r="D77">
-        <v>1870.567984999085</v>
+        <v>1851.634355909018</v>
       </c>
       <c r="E77">
-        <v>319.6999999999998</v>
+        <v>388.7240000000002</v>
       </c>
       <c r="F77">
-        <v>5176.8</v>
+        <v>5245.824000000001</v>
       </c>
       <c r="G77">
         <v>731.5</v>
@@ -7601,37 +7601,37 @@
         <v>488</v>
       </c>
       <c r="M77">
-        <v>1220.68944</v>
+        <v>1236.9652992</v>
       </c>
       <c r="N77">
-        <v>-732.6894400000001</v>
+        <v>-748.9652992000001</v>
       </c>
       <c r="O77">
-        <v>-109.903416</v>
+        <v>-112.34479488</v>
       </c>
       <c r="P77">
-        <v>-622.7860240000001</v>
+        <v>-636.6205043200001</v>
       </c>
       <c r="Q77">
-        <v>-306.7860240000001</v>
+        <v>-320.6205043200001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2109012759177067</v>
+        <v>0.2177804957476112</v>
       </c>
       <c r="T77">
-        <v>3.13191019546302</v>
+        <v>3.262406453607313</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.05996611226521301</v>
+        <v>0.05917708447224967</v>
       </c>
       <c r="W77">
-        <v>0.2216599907278628</v>
+        <v>0.2218460434814435</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3997740817680867</v>
+        <v>0.3945138964816645</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2208703120253238</v>
+        <v>0.2227703120253237</v>
       </c>
       <c r="C78">
-        <v>-2662.689644090982</v>
+        <v>-2750.267826762113</v>
       </c>
       <c r="D78">
-        <v>1851.634355909018</v>
+        <v>1833.080173237888</v>
       </c>
       <c r="E78">
-        <v>388.7240000000002</v>
+        <v>457.7480000000005</v>
       </c>
       <c r="F78">
-        <v>5245.824000000001</v>
+        <v>5314.848000000001</v>
       </c>
       <c r="G78">
         <v>731.5</v>
@@ -7683,37 +7683,37 @@
         <v>488</v>
       </c>
       <c r="M78">
-        <v>1236.9652992</v>
+        <v>1253.2411584</v>
       </c>
       <c r="N78">
-        <v>-748.9652992000001</v>
+        <v>-765.2411584000004</v>
       </c>
       <c r="O78">
-        <v>-112.34479488</v>
+        <v>-114.7861737600001</v>
       </c>
       <c r="P78">
-        <v>-636.6205043200001</v>
+        <v>-650.4549846400002</v>
       </c>
       <c r="Q78">
-        <v>-320.6205043200001</v>
+        <v>-334.4549846400002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2177804957476112</v>
+        <v>0.225257908606203</v>
       </c>
       <c r="T78">
-        <v>3.262406453607313</v>
+        <v>3.404250212459803</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.05917708447224967</v>
+        <v>0.05840855090767499</v>
       </c>
       <c r="W78">
-        <v>0.2218460434814435</v>
+        <v>0.2220272636959702</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3945138964816645</v>
+        <v>0.3893903393845</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2227703120253237</v>
+        <v>0.2246703120253238</v>
       </c>
       <c r="C79">
-        <v>-2750.267826762113</v>
+        <v>-2837.477856503748</v>
       </c>
       <c r="D79">
-        <v>1833.080173237888</v>
+        <v>1814.894143496253</v>
       </c>
       <c r="E79">
-        <v>457.7480000000005</v>
+        <v>526.7719999999999</v>
       </c>
       <c r="F79">
-        <v>5314.848000000001</v>
+        <v>5383.872</v>
       </c>
       <c r="G79">
         <v>731.5</v>
@@ -7765,37 +7765,37 @@
         <v>488</v>
       </c>
       <c r="M79">
-        <v>1253.2411584</v>
+        <v>1269.5170176</v>
       </c>
       <c r="N79">
-        <v>-765.2411584000004</v>
+        <v>-781.5170176000001</v>
       </c>
       <c r="O79">
-        <v>-114.7861737600001</v>
+        <v>-117.22755264</v>
       </c>
       <c r="P79">
-        <v>-650.4549846400002</v>
+        <v>-664.2894649600001</v>
       </c>
       <c r="Q79">
-        <v>-334.4549846400002</v>
+        <v>-348.2894649600001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.225257908606203</v>
+        <v>0.2334150862701213</v>
       </c>
       <c r="T79">
-        <v>3.404250212459803</v>
+        <v>3.558988858480704</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.05840855090767499</v>
+        <v>0.05765972333193557</v>
       </c>
       <c r="W79">
-        <v>0.2220272636959702</v>
+        <v>0.2222038372383296</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3893903393845</v>
+        <v>0.3843981555462372</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2246703120253238</v>
+        <v>0.2265703120253238</v>
       </c>
       <c r="C80">
-        <v>-2837.477856503748</v>
+        <v>-2924.330583036119</v>
       </c>
       <c r="D80">
-        <v>1814.894143496253</v>
+        <v>1797.065416963882</v>
       </c>
       <c r="E80">
-        <v>526.7719999999999</v>
+        <v>595.7960000000003</v>
       </c>
       <c r="F80">
-        <v>5383.872</v>
+        <v>5452.896000000001</v>
       </c>
       <c r="G80">
         <v>731.5</v>
@@ -7847,37 +7847,37 @@
         <v>488</v>
       </c>
       <c r="M80">
-        <v>1269.5170176</v>
+        <v>1285.7928768</v>
       </c>
       <c r="N80">
-        <v>-781.5170176000001</v>
+        <v>-797.7928768000002</v>
       </c>
       <c r="O80">
-        <v>-117.22755264</v>
+        <v>-119.66893152</v>
       </c>
       <c r="P80">
-        <v>-664.2894649600001</v>
+        <v>-678.1239452800002</v>
       </c>
       <c r="Q80">
-        <v>-348.2894649600001</v>
+        <v>-362.1239452800002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2334150862701213</v>
+        <v>0.24234913799727</v>
       </c>
       <c r="T80">
-        <v>3.558988858480704</v>
+        <v>3.728464518408358</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.05765972333193557</v>
+        <v>0.05692985341634145</v>
       </c>
       <c r="W80">
-        <v>0.2222038372383296</v>
+        <v>0.2223759405644267</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3843981555462372</v>
+        <v>0.3795323561089431</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2265703120253238</v>
+        <v>0.2284703120253238</v>
       </c>
       <c r="C81">
-        <v>-2924.330583036119</v>
+        <v>-3010.83643389518</v>
       </c>
       <c r="D81">
-        <v>1797.065416963882</v>
+        <v>1779.583566104821</v>
       </c>
       <c r="E81">
-        <v>595.7960000000003</v>
+        <v>664.8200000000006</v>
       </c>
       <c r="F81">
-        <v>5452.896000000001</v>
+        <v>5521.920000000001</v>
       </c>
       <c r="G81">
         <v>731.5</v>
@@ -7929,37 +7929,37 @@
         <v>488</v>
       </c>
       <c r="M81">
-        <v>1285.7928768</v>
+        <v>1302.068736</v>
       </c>
       <c r="N81">
-        <v>-797.7928768000002</v>
+        <v>-814.0687360000002</v>
       </c>
       <c r="O81">
-        <v>-119.66893152</v>
+        <v>-122.1103104</v>
       </c>
       <c r="P81">
-        <v>-678.1239452800002</v>
+        <v>-691.9584256000002</v>
       </c>
       <c r="Q81">
-        <v>-362.1239452800002</v>
+        <v>-375.9584256000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.24234913799727</v>
+        <v>0.2521765948971335</v>
       </c>
       <c r="T81">
-        <v>3.728464518408358</v>
+        <v>3.914887744328775</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05692985341634145</v>
+        <v>0.05621823024863719</v>
       </c>
       <c r="W81">
-        <v>0.2223759405644267</v>
+        <v>0.2225437413073714</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3795323561089431</v>
+        <v>0.3747882016575813</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2284703120253238</v>
+        <v>0.2303703120253238</v>
       </c>
       <c r="C82">
-        <v>-3010.83643389518</v>
+        <v>-3097.005434769808</v>
       </c>
       <c r="D82">
-        <v>1779.583566104821</v>
+        <v>1762.438565230192</v>
       </c>
       <c r="E82">
-        <v>664.8200000000006</v>
+        <v>733.8440000000001</v>
       </c>
       <c r="F82">
-        <v>5521.920000000001</v>
+        <v>5590.944</v>
       </c>
       <c r="G82">
         <v>731.5</v>
@@ -8011,37 +8011,37 @@
         <v>488</v>
       </c>
       <c r="M82">
-        <v>1302.068736</v>
+        <v>1318.3445952</v>
       </c>
       <c r="N82">
-        <v>-814.0687360000002</v>
+        <v>-830.3445952000002</v>
       </c>
       <c r="O82">
-        <v>-122.1103104</v>
+        <v>-124.55168928</v>
       </c>
       <c r="P82">
-        <v>-691.9584256000002</v>
+        <v>-705.7929059200002</v>
       </c>
       <c r="Q82">
-        <v>-375.9584256000002</v>
+        <v>-389.7929059200002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2521765948971335</v>
+        <v>0.263038520944351</v>
       </c>
       <c r="T82">
-        <v>3.914887744328775</v>
+        <v>4.1209344677145</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05621823024863719</v>
+        <v>0.05552417802334537</v>
       </c>
       <c r="W82">
-        <v>0.2225437413073714</v>
+        <v>0.2227073988220952</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3747882016575813</v>
+        <v>0.3701611868223025</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2303703120253238</v>
+        <v>0.2322703120253238</v>
       </c>
       <c r="C83">
-        <v>-3097.005434769808</v>
+        <v>-3182.847228674622</v>
       </c>
       <c r="D83">
-        <v>1762.438565230192</v>
+        <v>1745.620771325379</v>
       </c>
       <c r="E83">
-        <v>733.8440000000001</v>
+        <v>802.8680000000004</v>
       </c>
       <c r="F83">
-        <v>5590.944</v>
+        <v>5659.968000000001</v>
       </c>
       <c r="G83">
         <v>731.5</v>
@@ -8093,37 +8093,37 @@
         <v>488</v>
       </c>
       <c r="M83">
-        <v>1318.3445952</v>
+        <v>1334.6204544</v>
       </c>
       <c r="N83">
-        <v>-830.3445952000002</v>
+        <v>-846.6204544000002</v>
       </c>
       <c r="O83">
-        <v>-124.55168928</v>
+        <v>-126.99306816</v>
       </c>
       <c r="P83">
-        <v>-705.7929059200002</v>
+        <v>-719.6273862400002</v>
       </c>
       <c r="Q83">
-        <v>-389.7929059200002</v>
+        <v>-403.6273862400002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.263038520944351</v>
+        <v>0.2751073276634816</v>
       </c>
       <c r="T83">
-        <v>4.1209344677145</v>
+        <v>4.349875271476417</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05552417802334537</v>
+        <v>0.05484705390110945</v>
       </c>
       <c r="W83">
-        <v>0.2227073988220952</v>
+        <v>0.2228670646901184</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3701611868223025</v>
+        <v>0.3656470260073963</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2322703120253238</v>
+        <v>0.2341703120253238</v>
       </c>
       <c r="C84">
-        <v>-3182.847228674622</v>
+        <v>-3268.371094035443</v>
       </c>
       <c r="D84">
-        <v>1745.620771325379</v>
+        <v>1729.120905964558</v>
       </c>
       <c r="E84">
-        <v>802.8680000000004</v>
+        <v>871.8920000000007</v>
       </c>
       <c r="F84">
-        <v>5659.968000000001</v>
+        <v>5728.992000000001</v>
       </c>
       <c r="G84">
         <v>731.5</v>
@@ -8175,37 +8175,37 @@
         <v>488</v>
       </c>
       <c r="M84">
-        <v>1334.6204544</v>
+        <v>1350.8963136</v>
       </c>
       <c r="N84">
-        <v>-846.6204544000002</v>
+        <v>-862.8963136000002</v>
       </c>
       <c r="O84">
-        <v>-126.99306816</v>
+        <v>-129.43444704</v>
       </c>
       <c r="P84">
-        <v>-719.6273862400002</v>
+        <v>-733.4618665600002</v>
       </c>
       <c r="Q84">
-        <v>-403.6273862400002</v>
+        <v>-417.4618665600002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2751073276634816</v>
+        <v>0.2885959939966277</v>
       </c>
       <c r="T84">
-        <v>4.349875271476417</v>
+        <v>4.605750287445619</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05484705390110945</v>
+        <v>0.05418624602278283</v>
       </c>
       <c r="W84">
-        <v>0.2228670646901184</v>
+        <v>0.2230228831878278</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3656470260073963</v>
+        <v>0.3612416401518855</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2341703120253238</v>
+        <v>0.2360703120253238</v>
       </c>
       <c r="C85">
-        <v>-3268.371094035443</v>
+        <v>-3353.585961758694</v>
       </c>
       <c r="D85">
-        <v>1729.120905964558</v>
+        <v>1712.930038241308</v>
       </c>
       <c r="E85">
-        <v>871.8920000000007</v>
+        <v>940.9160000000011</v>
       </c>
       <c r="F85">
-        <v>5728.992000000001</v>
+        <v>5798.016000000001</v>
       </c>
       <c r="G85">
         <v>731.5</v>
@@ -8257,37 +8257,37 @@
         <v>488</v>
       </c>
       <c r="M85">
-        <v>1350.8963136</v>
+        <v>1367.1721728</v>
       </c>
       <c r="N85">
-        <v>-862.8963136000002</v>
+        <v>-879.1721728000005</v>
       </c>
       <c r="O85">
-        <v>-129.43444704</v>
+        <v>-131.8758259200001</v>
       </c>
       <c r="P85">
-        <v>-733.4618665600002</v>
+        <v>-747.2963468800003</v>
       </c>
       <c r="Q85">
-        <v>-417.4618665600002</v>
+        <v>-431.2963468800003</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2885959939966277</v>
+        <v>0.3037707436214169</v>
       </c>
       <c r="T85">
-        <v>4.605750287445619</v>
+        <v>4.893609680410971</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05418624602278283</v>
+        <v>0.05354117166536874</v>
       </c>
       <c r="W85">
-        <v>0.2230228831878278</v>
+        <v>0.2231749917213061</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3612416401518855</v>
+        <v>0.3569411444357916</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2360703120253238</v>
+        <v>0.2379703120253238</v>
       </c>
       <c r="C86">
-        <v>-3353.585961758693</v>
+        <v>-3438.500431350693</v>
       </c>
       <c r="D86">
-        <v>1712.930038241308</v>
+        <v>1697.039568649307</v>
       </c>
       <c r="E86">
-        <v>940.9160000000002</v>
+        <v>1009.94</v>
       </c>
       <c r="F86">
-        <v>5798.016000000001</v>
+        <v>5867.04</v>
       </c>
       <c r="G86">
         <v>731.5</v>
@@ -8339,37 +8339,37 @@
         <v>488</v>
       </c>
       <c r="M86">
-        <v>1367.1721728</v>
+        <v>1383.448032</v>
       </c>
       <c r="N86">
-        <v>-879.1721728000002</v>
+        <v>-895.448032</v>
       </c>
       <c r="O86">
-        <v>-131.87582592</v>
+        <v>-134.3172048</v>
       </c>
       <c r="P86">
-        <v>-747.2963468800002</v>
+        <v>-761.1308272</v>
       </c>
       <c r="Q86">
-        <v>-431.2963468800002</v>
+        <v>-445.1308272</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3037707436214168</v>
+        <v>0.3209687931961779</v>
       </c>
       <c r="T86">
-        <v>4.893609680410967</v>
+        <v>5.219850325771699</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05354117166536875</v>
+        <v>0.05291127552812912</v>
       </c>
       <c r="W86">
-        <v>0.2231749917213061</v>
+        <v>0.2233235212304672</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3569411444357916</v>
+        <v>0.3527418368541941</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2379703120253238</v>
+        <v>0.2398703120253237</v>
       </c>
       <c r="C87">
-        <v>-3438.500431350693</v>
+        <v>-3523.122786147999</v>
       </c>
       <c r="D87">
-        <v>1697.039568649307</v>
+        <v>1681.441213852001</v>
       </c>
       <c r="E87">
-        <v>1009.94</v>
+        <v>1078.964</v>
       </c>
       <c r="F87">
-        <v>5867.04</v>
+        <v>5936.064</v>
       </c>
       <c r="G87">
         <v>731.5</v>
@@ -8421,37 +8421,37 @@
         <v>488</v>
       </c>
       <c r="M87">
-        <v>1383.448032</v>
+        <v>1399.7238912</v>
       </c>
       <c r="N87">
-        <v>-895.448032</v>
+        <v>-911.7238912</v>
       </c>
       <c r="O87">
-        <v>-134.3172048</v>
+        <v>-136.75858368</v>
       </c>
       <c r="P87">
-        <v>-761.1308272</v>
+        <v>-774.96530752</v>
       </c>
       <c r="Q87">
-        <v>-445.1308272</v>
+        <v>-458.96530752</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3209687931961779</v>
+        <v>0.3406237069959049</v>
       </c>
       <c r="T87">
-        <v>5.219850325771699</v>
+        <v>5.592696777612534</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05291127552812912</v>
+        <v>0.05229602813826716</v>
       </c>
       <c r="W87">
-        <v>0.2233235212304672</v>
+        <v>0.2234685965649966</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3527418368541941</v>
+        <v>0.3486401875884477</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2398703120253237</v>
+        <v>0.2417703120253238</v>
       </c>
       <c r="C88">
-        <v>-3523.122786147999</v>
+        <v>-3607.461007715449</v>
       </c>
       <c r="D88">
-        <v>1681.441213852001</v>
+        <v>1666.126992284551</v>
       </c>
       <c r="E88">
-        <v>1078.964</v>
+        <v>1147.988</v>
       </c>
       <c r="F88">
-        <v>5936.064</v>
+        <v>6005.088000000001</v>
       </c>
       <c r="G88">
         <v>731.5</v>
@@ -8503,37 +8503,37 @@
         <v>488</v>
       </c>
       <c r="M88">
-        <v>1399.7238912</v>
+        <v>1415.9997504</v>
       </c>
       <c r="N88">
-        <v>-911.7238912</v>
+        <v>-927.9997504000003</v>
       </c>
       <c r="O88">
-        <v>-136.75858368</v>
+        <v>-139.19996256</v>
       </c>
       <c r="P88">
-        <v>-774.96530752</v>
+        <v>-788.7997878400002</v>
       </c>
       <c r="Q88">
-        <v>-458.96530752</v>
+        <v>-472.7997878400002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3406237069959049</v>
+        <v>0.3633024536878975</v>
       </c>
       <c r="T88">
-        <v>5.592696777612534</v>
+        <v>6.022904222044267</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05229602813826716</v>
+        <v>0.05169492436656293</v>
       </c>
       <c r="W88">
-        <v>0.2234685965649966</v>
+        <v>0.2236103368343645</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3486401875884477</v>
+        <v>0.3446328291104195</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2417703120253238</v>
+        <v>0.2436703120253238</v>
       </c>
       <c r="C89">
-        <v>-3607.461007715449</v>
+        <v>-3691.5227894645</v>
       </c>
       <c r="D89">
-        <v>1666.126992284551</v>
+        <v>1651.089210535501</v>
       </c>
       <c r="E89">
-        <v>1147.988</v>
+        <v>1217.012</v>
       </c>
       <c r="F89">
-        <v>6005.088000000001</v>
+        <v>6074.112</v>
       </c>
       <c r="G89">
         <v>731.5</v>
@@ -8585,37 +8585,37 @@
         <v>488</v>
       </c>
       <c r="M89">
-        <v>1415.9997504</v>
+        <v>1432.2756096</v>
       </c>
       <c r="N89">
-        <v>-927.9997504000003</v>
+        <v>-944.2756096000001</v>
       </c>
       <c r="O89">
-        <v>-139.19996256</v>
+        <v>-141.64134144</v>
       </c>
       <c r="P89">
-        <v>-788.7997878400002</v>
+        <v>-802.63426816</v>
       </c>
       <c r="Q89">
-        <v>-472.7997878400002</v>
+        <v>-486.63426816</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3633024536878975</v>
+        <v>0.3897609914952224</v>
       </c>
       <c r="T89">
-        <v>6.022904222044267</v>
+        <v>6.524812907214624</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05169492436656293</v>
+        <v>0.05110748204421563</v>
       </c>
       <c r="W89">
-        <v>0.2236103368343645</v>
+        <v>0.223748855733974</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3446328291104195</v>
+        <v>0.3407165469614375</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2436703120253238</v>
+        <v>0.2455703120253238</v>
       </c>
       <c r="C90">
-        <v>-3691.5227894645</v>
+        <v>-3775.31554954069</v>
       </c>
       <c r="D90">
-        <v>1651.089210535501</v>
+        <v>1636.32045045931</v>
       </c>
       <c r="E90">
-        <v>1217.012</v>
+        <v>1286.036</v>
       </c>
       <c r="F90">
-        <v>6074.112</v>
+        <v>6143.136</v>
       </c>
       <c r="G90">
         <v>731.5</v>
@@ -8667,37 +8667,37 @@
         <v>488</v>
       </c>
       <c r="M90">
-        <v>1432.2756096</v>
+        <v>1448.5514688</v>
       </c>
       <c r="N90">
-        <v>-944.2756096000001</v>
+        <v>-960.5514688000001</v>
       </c>
       <c r="O90">
-        <v>-141.64134144</v>
+        <v>-144.08272032</v>
       </c>
       <c r="P90">
-        <v>-802.63426816</v>
+        <v>-816.46874848</v>
       </c>
       <c r="Q90">
-        <v>-486.63426816</v>
+        <v>-500.46874848</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3897609914952224</v>
+        <v>0.4210301725402426</v>
       </c>
       <c r="T90">
-        <v>6.524812907214624</v>
+        <v>7.117977716961408</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05110748204421563</v>
+        <v>0.05053324067293231</v>
       </c>
       <c r="W90">
-        <v>0.223748855733974</v>
+        <v>0.2238842618493226</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3407165469614375</v>
+        <v>0.3368882711528821</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2455703120253238</v>
+        <v>0.2474703120253238</v>
       </c>
       <c r="C91">
-        <v>-3775.31554954069</v>
+        <v>-3858.846443025568</v>
       </c>
       <c r="D91">
-        <v>1636.32045045931</v>
+        <v>1621.813556974432</v>
       </c>
       <c r="E91">
-        <v>1286.036</v>
+        <v>1355.06</v>
       </c>
       <c r="F91">
-        <v>6143.136</v>
+        <v>6212.160000000001</v>
       </c>
       <c r="G91">
         <v>731.5</v>
@@ -8749,37 +8749,37 @@
         <v>488</v>
       </c>
       <c r="M91">
-        <v>1448.5514688</v>
+        <v>1464.827328</v>
       </c>
       <c r="N91">
-        <v>-960.5514688000001</v>
+        <v>-976.8273280000003</v>
       </c>
       <c r="O91">
-        <v>-144.08272032</v>
+        <v>-146.5240992000001</v>
       </c>
       <c r="P91">
-        <v>-816.46874848</v>
+        <v>-830.3032288000003</v>
       </c>
       <c r="Q91">
-        <v>-500.46874848</v>
+        <v>-514.3032288000003</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4210301725402426</v>
+        <v>0.458553189794267</v>
       </c>
       <c r="T91">
-        <v>7.117977716961408</v>
+        <v>7.829775488657551</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05053324067293231</v>
+        <v>0.04997176022101083</v>
       </c>
       <c r="W91">
-        <v>0.2238842618493226</v>
+        <v>0.2240166589398857</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3368882711528821</v>
+        <v>0.3331450681400722</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2474703120253238</v>
+        <v>0.2493703120253238</v>
       </c>
       <c r="C92">
-        <v>-3858.846443025568</v>
+        <v>-3942.12237349526</v>
       </c>
       <c r="D92">
-        <v>1621.813556974432</v>
+        <v>1607.561626504742</v>
       </c>
       <c r="E92">
-        <v>1355.06</v>
+        <v>1424.084000000001</v>
       </c>
       <c r="F92">
-        <v>6212.160000000001</v>
+        <v>6281.184000000001</v>
       </c>
       <c r="G92">
         <v>731.5</v>
@@ -8831,37 +8831,37 @@
         <v>488</v>
       </c>
       <c r="M92">
-        <v>1464.827328</v>
+        <v>1481.1031872</v>
       </c>
       <c r="N92">
-        <v>-976.8273280000003</v>
+        <v>-993.1031872000003</v>
       </c>
       <c r="O92">
-        <v>-146.5240992000001</v>
+        <v>-148.9654780800001</v>
       </c>
       <c r="P92">
-        <v>-830.3032288000003</v>
+        <v>-844.1377091200003</v>
       </c>
       <c r="Q92">
-        <v>-514.3032288000003</v>
+        <v>-528.1377091200003</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.458553189794267</v>
+        <v>0.5044146553269633</v>
       </c>
       <c r="T92">
-        <v>7.829775488657551</v>
+        <v>8.699750542952835</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04997176022101083</v>
+        <v>0.04942261999880192</v>
       </c>
       <c r="W92">
-        <v>0.2240166589398857</v>
+        <v>0.2241461462042825</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3331450681400722</v>
+        <v>0.3294841333253461</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2493703120253238</v>
+        <v>0.2512703120253238</v>
       </c>
       <c r="C93">
-        <v>-3942.12237349526</v>
+        <v>-4025.150003974917</v>
       </c>
       <c r="D93">
-        <v>1607.561626504742</v>
+        <v>1593.557996025083</v>
       </c>
       <c r="E93">
-        <v>1424.084000000001</v>
+        <v>1493.108</v>
       </c>
       <c r="F93">
-        <v>6281.184000000001</v>
+        <v>6350.208000000001</v>
       </c>
       <c r="G93">
         <v>731.5</v>
@@ -8913,37 +8913,37 @@
         <v>488</v>
       </c>
       <c r="M93">
-        <v>1481.1031872</v>
+        <v>1497.3790464</v>
       </c>
       <c r="N93">
-        <v>-993.1031872000003</v>
+        <v>-1009.3790464</v>
       </c>
       <c r="O93">
-        <v>-148.9654780800001</v>
+        <v>-151.40685696</v>
       </c>
       <c r="P93">
-        <v>-844.1377091200003</v>
+        <v>-857.9721894400001</v>
       </c>
       <c r="Q93">
-        <v>-528.1377091200003</v>
+        <v>-541.9721894400001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5044146553269633</v>
+        <v>0.5617414872428338</v>
       </c>
       <c r="T93">
-        <v>8.699750542952835</v>
+        <v>9.787219360821942</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04942261999880192</v>
+        <v>0.0488854176075106</v>
       </c>
       <c r="W93">
-        <v>0.2241461462042825</v>
+        <v>0.224272818528149</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3294841333253461</v>
+        <v>0.3259027840500707</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2512703120253238</v>
+        <v>0.2531703120253238</v>
       </c>
       <c r="C94">
-        <v>-4025.150003974917</v>
+        <v>-4107.935767325558</v>
       </c>
       <c r="D94">
-        <v>1593.557996025083</v>
+        <v>1579.796232674443</v>
       </c>
       <c r="E94">
-        <v>1493.108</v>
+        <v>1562.132000000001</v>
       </c>
       <c r="F94">
-        <v>6350.208000000001</v>
+        <v>6419.232000000001</v>
       </c>
       <c r="G94">
         <v>731.5</v>
@@ -8995,37 +8995,37 @@
         <v>488</v>
       </c>
       <c r="M94">
-        <v>1497.3790464</v>
+        <v>1513.6549056</v>
       </c>
       <c r="N94">
-        <v>-1009.3790464</v>
+        <v>-1025.6549056</v>
       </c>
       <c r="O94">
-        <v>-151.40685696</v>
+        <v>-153.8482358400001</v>
       </c>
       <c r="P94">
-        <v>-857.9721894400001</v>
+        <v>-871.8066697600003</v>
       </c>
       <c r="Q94">
-        <v>-541.9721894400001</v>
+        <v>-555.8066697600003</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5617414872428338</v>
+        <v>0.6354474139918102</v>
       </c>
       <c r="T94">
-        <v>9.787219360821942</v>
+        <v>11.18539355522508</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0488854176075106</v>
+        <v>0.04835976795581693</v>
       </c>
       <c r="W94">
-        <v>0.224272818528149</v>
+        <v>0.2243967667160184</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3259027840500707</v>
+        <v>0.3223984530387796</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2531703120253238</v>
+        <v>0.2550703120253238</v>
       </c>
       <c r="C95">
-        <v>-4107.935767325558</v>
+        <v>-4190.485876097309</v>
       </c>
       <c r="D95">
-        <v>1579.796232674443</v>
+        <v>1566.270123902692</v>
       </c>
       <c r="E95">
-        <v>1562.132000000001</v>
+        <v>1631.156000000001</v>
       </c>
       <c r="F95">
-        <v>6419.232000000001</v>
+        <v>6488.256000000001</v>
       </c>
       <c r="G95">
         <v>731.5</v>
@@ -9077,37 +9077,37 @@
         <v>488</v>
       </c>
       <c r="M95">
-        <v>1513.6549056</v>
+        <v>1529.9307648</v>
       </c>
       <c r="N95">
-        <v>-1025.6549056</v>
+        <v>-1041.9307648</v>
       </c>
       <c r="O95">
-        <v>-153.8482358400001</v>
+        <v>-156.2896147200001</v>
       </c>
       <c r="P95">
-        <v>-871.8066697600003</v>
+        <v>-885.6411500800003</v>
       </c>
       <c r="Q95">
-        <v>-555.8066697600003</v>
+        <v>-569.6411500800003</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6354474139918102</v>
+        <v>0.7337219829904453</v>
       </c>
       <c r="T95">
-        <v>11.18539355522508</v>
+        <v>13.04962581442926</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04835976795581693</v>
+        <v>0.04784530233926569</v>
       </c>
       <c r="W95">
-        <v>0.2243967667160184</v>
+        <v>0.2245180777084012</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3223984530387796</v>
+        <v>0.3189686822617712</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2550703120253238</v>
+        <v>0.2569703120253238</v>
       </c>
       <c r="C96">
-        <v>-4190.485876097309</v>
+        <v>-4272.806331880776</v>
       </c>
       <c r="D96">
-        <v>1566.270123902692</v>
+        <v>1552.973668119225</v>
       </c>
       <c r="E96">
-        <v>1631.156000000001</v>
+        <v>1700.18</v>
       </c>
       <c r="F96">
-        <v>6488.256000000001</v>
+        <v>6557.280000000001</v>
       </c>
       <c r="G96">
         <v>731.5</v>
@@ -9159,37 +9159,37 @@
         <v>488</v>
       </c>
       <c r="M96">
-        <v>1529.9307648</v>
+        <v>1546.206624</v>
       </c>
       <c r="N96">
-        <v>-1041.9307648</v>
+        <v>-1058.206624</v>
       </c>
       <c r="O96">
-        <v>-156.2896147200001</v>
+        <v>-158.7309936</v>
       </c>
       <c r="P96">
-        <v>-885.6411500800003</v>
+        <v>-899.4756304000001</v>
       </c>
       <c r="Q96">
-        <v>-569.6411500800003</v>
+        <v>-583.4756304000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7337219829904453</v>
+        <v>0.8713063795885347</v>
       </c>
       <c r="T96">
-        <v>13.04962581442926</v>
+        <v>15.65955097731512</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04784530233926569</v>
+        <v>0.04734166757779974</v>
       </c>
       <c r="W96">
-        <v>0.2245180777084012</v>
+        <v>0.2246368347851548</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3189686822617712</v>
+        <v>0.3156111171853316</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2569703120253238</v>
+        <v>0.2588703120253238</v>
       </c>
       <c r="C97">
-        <v>-4272.806331880776</v>
+        <v>-4354.902934186112</v>
       </c>
       <c r="D97">
-        <v>1552.973668119225</v>
+        <v>1539.901065813888</v>
       </c>
       <c r="E97">
-        <v>1700.18</v>
+        <v>1769.204000000001</v>
       </c>
       <c r="F97">
-        <v>6557.280000000001</v>
+        <v>6626.304000000001</v>
       </c>
       <c r="G97">
         <v>731.5</v>
@@ -9241,37 +9241,37 @@
         <v>488</v>
       </c>
       <c r="M97">
-        <v>1546.206624</v>
+        <v>1562.4824832</v>
       </c>
       <c r="N97">
-        <v>-1058.206624</v>
+        <v>-1074.4824832</v>
       </c>
       <c r="O97">
-        <v>-158.7309936</v>
+        <v>-161.1723724800001</v>
       </c>
       <c r="P97">
-        <v>-899.4756304000001</v>
+        <v>-913.3101107200004</v>
       </c>
       <c r="Q97">
-        <v>-583.4756304000001</v>
+        <v>-597.3101107200004</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8713063795885347</v>
+        <v>1.077682974485669</v>
       </c>
       <c r="T97">
-        <v>15.65955097731512</v>
+        <v>19.57443872164391</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04734166757779974</v>
+        <v>0.04684852520719766</v>
       </c>
       <c r="W97">
-        <v>0.2246368347851548</v>
+        <v>0.2247531177561428</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3156111171853316</v>
+        <v>0.3123235013813177</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2588703120253238</v>
+        <v>0.2607703120253238</v>
       </c>
       <c r="C98">
-        <v>-4354.902934186111</v>
+        <v>-4436.781288877362</v>
       </c>
       <c r="D98">
-        <v>1539.901065813888</v>
+        <v>1527.046711122638</v>
       </c>
       <c r="E98">
-        <v>1769.204</v>
+        <v>1838.228</v>
       </c>
       <c r="F98">
-        <v>6626.304</v>
+        <v>6695.328</v>
       </c>
       <c r="G98">
         <v>731.5</v>
@@ -9323,37 +9323,37 @@
         <v>488</v>
       </c>
       <c r="M98">
-        <v>1562.4824832</v>
+        <v>1578.7583424</v>
       </c>
       <c r="N98">
-        <v>-1074.4824832</v>
+        <v>-1090.7583424</v>
       </c>
       <c r="O98">
-        <v>-161.17237248</v>
+        <v>-163.61375136</v>
       </c>
       <c r="P98">
-        <v>-913.3101107200001</v>
+        <v>-927.1445910400001</v>
       </c>
       <c r="Q98">
-        <v>-597.3101107200001</v>
+        <v>-611.1445910400001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.077682974485666</v>
+        <v>1.421643965980888</v>
       </c>
       <c r="T98">
-        <v>19.57443872164386</v>
+        <v>26.09925162885848</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04684852520719766</v>
+        <v>0.04636555072052551</v>
       </c>
       <c r="W98">
-        <v>0.2247531177561428</v>
+        <v>0.2248670031401001</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3123235013813177</v>
+        <v>0.3091036714701701</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2607703120253238</v>
+        <v>0.2626703120253238</v>
       </c>
       <c r="C99">
-        <v>-4436.781288877362</v>
+        <v>-4518.446816187886</v>
       </c>
       <c r="D99">
-        <v>1527.046711122638</v>
+        <v>1514.405183812115</v>
       </c>
       <c r="E99">
-        <v>1838.228</v>
+        <v>1907.252</v>
       </c>
       <c r="F99">
-        <v>6695.328</v>
+        <v>6764.352000000001</v>
       </c>
       <c r="G99">
         <v>731.5</v>
@@ -9405,37 +9405,37 @@
         <v>488</v>
       </c>
       <c r="M99">
-        <v>1578.7583424</v>
+        <v>1595.0342016</v>
       </c>
       <c r="N99">
-        <v>-1090.7583424</v>
+        <v>-1107.0342016</v>
       </c>
       <c r="O99">
-        <v>-163.61375136</v>
+        <v>-166.05513024</v>
       </c>
       <c r="P99">
-        <v>-927.1445910400001</v>
+        <v>-940.9790713600001</v>
       </c>
       <c r="Q99">
-        <v>-611.1445910400001</v>
+        <v>-624.9790713600001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.421643965980888</v>
+        <v>2.109565948971332</v>
       </c>
       <c r="T99">
-        <v>26.09925162885848</v>
+        <v>39.14887744328771</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04636555072052551</v>
+        <v>0.04589243285603035</v>
       </c>
       <c r="W99">
-        <v>0.2248670031401001</v>
+        <v>0.224978564332548</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3091036714701701</v>
+        <v>0.3059495523735357</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2626703120253238</v>
+        <v>0.2645703120253238</v>
       </c>
       <c r="C100">
-        <v>-4518.446816187886</v>
+        <v>-4599.904758340903</v>
       </c>
       <c r="D100">
-        <v>1514.405183812115</v>
+        <v>1501.971241659098</v>
       </c>
       <c r="E100">
-        <v>1907.252</v>
+        <v>1976.276</v>
       </c>
       <c r="F100">
-        <v>6764.352000000001</v>
+        <v>6833.376</v>
       </c>
       <c r="G100">
         <v>731.5</v>
@@ -9487,37 +9487,37 @@
         <v>488</v>
       </c>
       <c r="M100">
-        <v>1595.0342016</v>
+        <v>1611.3100608</v>
       </c>
       <c r="N100">
-        <v>-1107.0342016</v>
+        <v>-1123.3100608</v>
       </c>
       <c r="O100">
-        <v>-166.05513024</v>
+        <v>-168.49650912</v>
       </c>
       <c r="P100">
-        <v>-940.9790713600001</v>
+        <v>-954.8135516800002</v>
       </c>
       <c r="Q100">
-        <v>-624.9790713600001</v>
+        <v>-638.8135516800002</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.109565948971332</v>
+        <v>4.173331897942664</v>
       </c>
       <c r="T100">
-        <v>39.14887744328771</v>
+        <v>78.29775488657542</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04589243285603035</v>
+        <v>0.04542887292819166</v>
       </c>
       <c r="W100">
-        <v>0.224978564332548</v>
+        <v>0.2250878717635324</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3059495523735357</v>
+        <v>0.3028591528546111</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2645703120253238</v>
-      </c>
-      <c r="C101">
-        <v>-4599.904758340903</v>
-      </c>
-      <c r="D101">
-        <v>1501.971241659098</v>
-      </c>
-      <c r="E101">
-        <v>1976.276</v>
-      </c>
-      <c r="F101">
-        <v>6833.376</v>
-      </c>
-      <c r="G101">
-        <v>731.5</v>
-      </c>
-      <c r="H101">
-        <v>2045.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>804</v>
-      </c>
-      <c r="K101">
-        <v>316</v>
-      </c>
-      <c r="L101">
-        <v>488</v>
-      </c>
-      <c r="M101">
-        <v>1611.3100608</v>
-      </c>
-      <c r="N101">
-        <v>-1123.3100608</v>
-      </c>
-      <c r="O101">
-        <v>-168.49650912</v>
-      </c>
-      <c r="P101">
-        <v>-954.8135516800002</v>
-      </c>
-      <c r="Q101">
-        <v>-638.8135516800002</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.173331897942664</v>
-      </c>
-      <c r="T101">
-        <v>78.29775488657542</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04542887292819166</v>
-      </c>
-      <c r="W101">
-        <v>0.2250878717635324</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3028591528546111</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
